--- a/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>NTRB</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44135</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44043</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43951</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43861</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43769</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43677</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43585</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43496</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43404</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43312</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43220</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43131</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43039</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42947</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42855</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
         <v>700</v>
-      </c>
-      <c r="E8" s="3">
-        <v>500</v>
       </c>
       <c r="F8" s="3">
         <v>500</v>
       </c>
       <c r="G8" s="3">
+        <v>500</v>
+      </c>
+      <c r="H8" s="3">
         <v>600</v>
-      </c>
-      <c r="H8" s="3">
-        <v>500</v>
       </c>
       <c r="I8" s="3">
         <v>500</v>
@@ -805,44 +809,44 @@
         <v>500</v>
       </c>
       <c r="K8" s="3">
+        <v>500</v>
+      </c>
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
-      </c>
-      <c r="M8" s="3">
-        <v>400</v>
       </c>
       <c r="N8" s="3">
         <v>400</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="P8" s="3">
         <v>100</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <v>100</v>
       </c>
       <c r="T8" s="3">
+        <v>100</v>
+      </c>
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
-        <v>100</v>
-      </c>
       <c r="V8" s="3">
+        <v>100</v>
+      </c>
+      <c r="W8" s="3">
         <v>200</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
@@ -858,25 +862,28 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>300</v>
       </c>
       <c r="H9" s="3">
         <v>300</v>
@@ -885,10 +892,10 @@
         <v>300</v>
       </c>
       <c r="J9" s="3">
+        <v>300</v>
+      </c>
+      <c r="K9" s="3">
         <v>400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>200</v>
       </c>
       <c r="L9" s="3">
         <v>200</v>
@@ -900,7 +907,7 @@
         <v>200</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P9" s="3">
         <v>100</v>
@@ -915,17 +922,17 @@
         <v>100</v>
       </c>
       <c r="T9" s="3">
+        <v>100</v>
+      </c>
+      <c r="U9" s="3">
         <v>200</v>
       </c>
-      <c r="U9" s="3">
-        <v>100</v>
-      </c>
       <c r="V9" s="3">
+        <v>100</v>
+      </c>
+      <c r="W9" s="3">
         <v>200</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -944,56 +951,59 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
       <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
         <v>300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>200</v>
       </c>
       <c r="J10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P10" s="3">
         <v>0</v>
       </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
         <v>-100</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
@@ -1006,8 +1016,8 @@
       <c r="V10" s="3">
         <v>0</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
+      <c r="W10" s="3">
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
@@ -1027,8 +1037,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1058,19 +1071,20 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E12" s="3">
         <v>400</v>
       </c>
       <c r="F12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G12" s="3">
         <v>300</v>
@@ -1079,17 +1093,17 @@
         <v>300</v>
       </c>
       <c r="I12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="J12" s="3">
+        <v>100</v>
+      </c>
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1141,8 +1155,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1224,8 +1241,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1235,12 +1255,12 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1248,11 +1268,11 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1266,10 +1286,10 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>100</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1280,11 +1300,11 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1292,12 +1312,12 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2500</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1307,8 +1327,11 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1390,8 +1413,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1418,174 +1444,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="E17" s="3">
         <v>1500</v>
       </c>
       <c r="F17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>700</v>
       </c>
       <c r="M17" s="3">
         <v>700</v>
       </c>
       <c r="N17" s="3">
+        <v>700</v>
+      </c>
+      <c r="O17" s="3">
         <v>400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>300</v>
       </c>
       <c r="P17" s="3">
         <v>300</v>
       </c>
       <c r="Q17" s="3">
+        <v>300</v>
+      </c>
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2400</v>
       </c>
-      <c r="Z17" s="3">
-        <v>100</v>
-      </c>
       <c r="AA17" s="3">
         <v>100</v>
       </c>
       <c r="AB17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P18" s="3">
         <v>-200</v>
       </c>
       <c r="Q18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-500</v>
       </c>
       <c r="V18" s="3">
         <v>-500</v>
       </c>
       <c r="W18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X18" s="3">
         <v>-1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-100</v>
       </c>
       <c r="AA18" s="3">
         <v>-100</v>
       </c>
       <c r="AB18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1615,8 +1648,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,14 +1694,14 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1695,85 +1729,88 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1000</v>
       </c>
       <c r="H21" s="3">
         <v>-1000</v>
       </c>
       <c r="I21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
         <v>-200</v>
       </c>
       <c r="Q21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>0</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
@@ -1781,8 +1818,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1792,11 +1832,11 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1823,13 +1863,13 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>100</v>
-      </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1837,8 +1877,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1849,8 +1889,8 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1864,91 +1904,97 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-500</v>
       </c>
       <c r="V23" s="3">
         <v>-500</v>
       </c>
       <c r="W23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-100</v>
       </c>
       <c r="AA23" s="3">
         <v>-100</v>
       </c>
       <c r="AB23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2030,8 +2076,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2113,174 +2162,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-500</v>
       </c>
       <c r="V26" s="3">
         <v>-500</v>
       </c>
       <c r="W26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X26" s="3">
         <v>-1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-100</v>
       </c>
       <c r="AA26" s="3">
         <v>-100</v>
       </c>
       <c r="AB26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-500</v>
       </c>
       <c r="V27" s="3">
         <v>-500</v>
       </c>
       <c r="W27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X27" s="3">
         <v>-1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-100</v>
       </c>
       <c r="AA27" s="3">
         <v>-100</v>
       </c>
       <c r="AB27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2362,8 +2420,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2445,8 +2506,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2528,8 +2592,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2611,8 +2678,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2656,14 +2726,14 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2691,94 +2761,100 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-500</v>
       </c>
       <c r="V33" s="3">
         <v>-500</v>
       </c>
       <c r="W33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X33" s="3">
         <v>-1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-100</v>
       </c>
       <c r="AA33" s="3">
         <v>-100</v>
       </c>
       <c r="AB33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2860,179 +2936,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-500</v>
       </c>
       <c r="V35" s="3">
         <v>-500</v>
       </c>
       <c r="W35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X35" s="3">
         <v>-1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-100</v>
       </c>
       <c r="AA35" s="3">
         <v>-100</v>
       </c>
       <c r="AB35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44135</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44043</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43951</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43861</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43769</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43677</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43585</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43496</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43404</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43312</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43220</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43131</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43039</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42947</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42855</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3062,8 +3147,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3093,46 +3179,47 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>300</v>
-      </c>
-      <c r="M41" s="3">
-        <v>200</v>
       </c>
       <c r="N41" s="3">
         <v>200</v>
       </c>
       <c r="O41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P41" s="3">
         <v>0</v>
@@ -3141,26 +3228,26 @@
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1100</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
         <v>0</v>
       </c>
@@ -3173,11 +3260,14 @@
       <c r="AB41" s="3">
         <v>0</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3259,8 +3349,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3271,7 +3364,7 @@
         <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
@@ -3289,16 +3382,16 @@
         <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3307,22 +3400,22 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3">
         <v>100</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3339,11 +3432,14 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3363,7 +3459,7 @@
         <v>200</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
         <v>100</v>
@@ -3378,10 +3474,10 @@
         <v>100</v>
       </c>
       <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
@@ -3398,17 +3494,17 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
       <c r="W44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3422,19 +3518,22 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
       </c>
       <c r="F45" s="3">
         <v>400</v>
@@ -3443,25 +3542,25 @@
         <v>400</v>
       </c>
       <c r="H45" s="3">
+        <v>400</v>
+      </c>
+      <c r="I45" s="3">
         <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
       </c>
       <c r="J45" s="3">
         <v>400</v>
       </c>
       <c r="K45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3">
-        <v>0</v>
+      <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
@@ -3473,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="R45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -3494,105 +3593,111 @@
         <v>100</v>
       </c>
       <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>600</v>
-      </c>
-      <c r="M46" s="3">
-        <v>300</v>
       </c>
       <c r="N46" s="3">
         <v>300</v>
       </c>
       <c r="O46" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P46" s="3">
         <v>100</v>
       </c>
       <c r="Q46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3">
         <v>300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1200</v>
       </c>
-      <c r="X46" s="3">
-        <v>100</v>
-      </c>
       <c r="Y46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3">
-        <v>0</v>
-      </c>
       <c r="AA46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3674,31 +3779,34 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E48" s="3">
         <v>900</v>
       </c>
       <c r="F48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G48" s="3">
         <v>1000</v>
       </c>
       <c r="H48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I48" s="3">
         <v>1100</v>
       </c>
       <c r="J48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="K48" s="3">
         <v>1000</v>
@@ -3707,14 +3815,14 @@
         <v>1000</v>
       </c>
       <c r="M48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N48" s="3">
         <v>1100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1300</v>
       </c>
-      <c r="O48" s="3">
-        <v>100</v>
-      </c>
       <c r="P48" s="3">
         <v>100</v>
       </c>
@@ -3737,10 +3845,10 @@
         <v>100</v>
       </c>
       <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -3757,8 +3865,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3766,13 +3877,13 @@
         <v>5700</v>
       </c>
       <c r="E49" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="F49" s="3">
         <v>5800</v>
       </c>
       <c r="G49" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="H49" s="3">
         <v>6200</v>
@@ -3781,10 +3892,10 @@
         <v>6200</v>
       </c>
       <c r="J49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K49" s="3">
         <v>6300</v>
-      </c>
-      <c r="K49" s="3">
-        <v>8500</v>
       </c>
       <c r="L49" s="3">
         <v>8500</v>
@@ -3796,7 +3907,7 @@
         <v>8500</v>
       </c>
       <c r="O49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="P49" s="3">
         <v>2000</v>
@@ -3808,7 +3919,7 @@
         <v>2000</v>
       </c>
       <c r="S49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="T49" s="3">
         <v>2100</v>
@@ -3819,8 +3930,8 @@
       <c r="V49" s="3">
         <v>2100</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3">
+        <v>2100</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -3828,20 +3939,23 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA49" s="3">
         <v>2400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2500</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3923,8 +4037,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4006,8 +4123,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4065,15 +4185,15 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3">
         <v>1900</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4089,8 +4209,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4172,46 +4295,49 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E54" s="3">
         <v>9900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10100</v>
-      </c>
-      <c r="O54" s="3">
-        <v>2200</v>
       </c>
       <c r="P54" s="3">
         <v>2200</v>
@@ -4220,43 +4346,46 @@
         <v>2200</v>
       </c>
       <c r="R54" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="S54" s="3">
         <v>2400</v>
       </c>
       <c r="T54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="U54" s="3">
         <v>2500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3100</v>
       </c>
-      <c r="X54" s="3">
-        <v>100</v>
-      </c>
       <c r="Y54" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z54" s="3">
         <v>200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2500</v>
       </c>
-      <c r="AB54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4286,8 +4415,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4317,13 +4447,14 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E57" s="3">
         <v>500</v>
@@ -4335,58 +4466,58 @@
         <v>500</v>
       </c>
       <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>600</v>
       </c>
       <c r="K57" s="3">
         <v>600</v>
       </c>
       <c r="L57" s="3">
+        <v>600</v>
+      </c>
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>700</v>
       </c>
       <c r="P57" s="3">
         <v>700</v>
       </c>
       <c r="Q57" s="3">
+        <v>700</v>
+      </c>
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
-        <v>100</v>
-      </c>
       <c r="X57" s="3">
         <v>100</v>
       </c>
       <c r="Y57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
@@ -4397,11 +4528,14 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4409,7 +4543,7 @@
         <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -4427,34 +4561,34 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>100</v>
+      </c>
+      <c r="M58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1600</v>
       </c>
-      <c r="O58" s="3">
-        <v>100</v>
-      </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3">
-        <v>100</v>
-      </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -4468,31 +4602,34 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
+      <c r="Y58" s="3">
+        <v>0</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>200</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
@@ -4507,14 +4644,14 @@
         <v>200</v>
       </c>
       <c r="J59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
-        <v>100</v>
-      </c>
       <c r="M59" s="3">
         <v>100</v>
       </c>
@@ -4522,28 +4659,28 @@
         <v>100</v>
       </c>
       <c r="O59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
       </c>
       <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>500</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
       <c r="T59" s="3">
         <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -4563,70 +4700,73 @@
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
         <v>900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>800</v>
       </c>
       <c r="H60" s="3">
         <v>800</v>
       </c>
       <c r="I60" s="3">
+        <v>800</v>
+      </c>
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2700</v>
-      </c>
-      <c r="M60" s="3">
-        <v>2600</v>
       </c>
       <c r="N60" s="3">
         <v>2600</v>
       </c>
       <c r="O60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
-      </c>
-      <c r="T60" s="3">
-        <v>400</v>
       </c>
       <c r="U60" s="3">
         <v>400</v>
       </c>
       <c r="V60" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="W60" s="3">
         <v>200</v>
@@ -4635,7 +4775,7 @@
         <v>200</v>
       </c>
       <c r="Y60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z60" s="3">
         <v>0</v>
@@ -4646,11 +4786,14 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4658,7 +4801,7 @@
         <v>2100</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -4679,17 +4822,17 @@
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>200</v>
       </c>
       <c r="N61" s="3">
+        <v>200</v>
+      </c>
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4732,8 +4875,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4750,13 +4896,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>100</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -4773,8 +4919,8 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -4815,8 +4961,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4898,8 +5047,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4981,8 +5133,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5064,37 +5219,40 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>900</v>
       </c>
       <c r="G66" s="3">
         <v>900</v>
       </c>
       <c r="H66" s="3">
+        <v>900</v>
+      </c>
+      <c r="I66" s="3">
         <v>1000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>900</v>
       </c>
       <c r="J66" s="3">
         <v>900</v>
       </c>
       <c r="K66" s="3">
+        <v>900</v>
+      </c>
+      <c r="L66" s="3">
         <v>1100</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2800</v>
       </c>
       <c r="M66" s="3">
         <v>2800</v>
@@ -5103,28 +5261,28 @@
         <v>2800</v>
       </c>
       <c r="O66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P66" s="3">
         <v>900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>700</v>
-      </c>
-      <c r="T66" s="3">
-        <v>400</v>
       </c>
       <c r="U66" s="3">
         <v>400</v>
       </c>
       <c r="V66" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="W66" s="3">
         <v>200</v>
@@ -5133,7 +5291,7 @@
         <v>200</v>
       </c>
       <c r="Y66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z66" s="3">
         <v>0</v>
@@ -5144,11 +5302,14 @@
       <c r="AB66" s="3">
         <v>0</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5178,8 +5339,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5261,8 +5423,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5344,8 +5509,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5427,8 +5595,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5510,91 +5681,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-24300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-23500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-22500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-20800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-19700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-18700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-18000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-14200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-9600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-9500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-7200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5676,8 +5853,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5759,8 +5939,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5842,91 +6025,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E76" s="3">
         <v>6900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2100</v>
-      </c>
-      <c r="U76" s="3">
-        <v>2400</v>
       </c>
       <c r="V76" s="3">
         <v>2400</v>
       </c>
       <c r="W76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X76" s="3">
         <v>2900</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
       <c r="Y76" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA76" s="3">
         <v>2400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2500</v>
       </c>
-      <c r="AB76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6008,179 +6197,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44135</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44043</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43951</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43861</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43769</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43677</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43585</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43496</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43404</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43312</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43220</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43131</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43039</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42947</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42855</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-500</v>
       </c>
       <c r="V81" s="3">
         <v>-500</v>
       </c>
       <c r="W81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X81" s="3">
         <v>-1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-100</v>
       </c>
       <c r="AA81" s="3">
         <v>-100</v>
       </c>
       <c r="AB81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6210,8 +6408,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6233,21 +6432,21 @@
       <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>100</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -6270,10 +6469,10 @@
         <v>0</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>100</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -6281,11 +6480,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>100</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
@@ -6293,8 +6492,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6376,8 +6578,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6459,8 +6664,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6542,8 +6750,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6625,8 +6836,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6708,73 +6922,76 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
       <c r="N89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
+        <v>100</v>
+      </c>
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-300</v>
       </c>
       <c r="U89" s="3">
         <v>-300</v>
       </c>
       <c r="V89" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="W89" s="3">
         <v>-400</v>
       </c>
       <c r="X89" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
@@ -6788,11 +7005,14 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6822,8 +7042,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6854,8 +7075,8 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -6872,8 +7093,8 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -6905,8 +7126,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6988,8 +7212,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7071,8 +7298,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7094,29 +7324,29 @@
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -7131,11 +7361,11 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -7151,11 +7381,14 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7185,8 +7418,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7268,8 +7502,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7351,8 +7588,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7434,8 +7674,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7517,17 +7760,20 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>2100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -7535,56 +7781,56 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
-        <v>100</v>
-      </c>
       <c r="T100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>1500</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -7597,11 +7843,14 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7680,77 +7929,80 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
-        <v>100</v>
-      </c>
       <c r="N102" s="3">
+        <v>100</v>
+      </c>
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
-        <v>100</v>
-      </c>
       <c r="S102" s="3">
+        <v>100</v>
+      </c>
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1100</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
@@ -7763,7 +8015,10 @@
       <c r="AB102" s="3">
         <v>0</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>NTRB</t>
   </si>
@@ -656,134 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -791,55 +798,55 @@
         <v>400</v>
       </c>
       <c r="E8" s="3">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3">
+        <v>400</v>
+      </c>
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>500</v>
-      </c>
-      <c r="H8" s="3">
-        <v>600</v>
       </c>
       <c r="I8" s="3">
         <v>500</v>
       </c>
       <c r="J8" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K8" s="3">
         <v>500</v>
       </c>
       <c r="L8" s="3">
+        <v>500</v>
+      </c>
+      <c r="M8" s="3">
+        <v>500</v>
+      </c>
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>100</v>
-      </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8" s="3">
         <v>100</v>
       </c>
       <c r="T8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
@@ -848,10 +855,10 @@
         <v>200</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -865,19 +872,25 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
         <v>300</v>
-      </c>
-      <c r="E9" s="3">
-        <v>400</v>
       </c>
       <c r="F9" s="3">
         <v>300</v>
@@ -889,19 +902,19 @@
         <v>300</v>
       </c>
       <c r="I9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J9" s="3">
         <v>300</v>
       </c>
       <c r="K9" s="3">
+        <v>300</v>
+      </c>
+      <c r="L9" s="3">
+        <v>300</v>
+      </c>
+      <c r="M9" s="3">
         <v>400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>200</v>
-      </c>
-      <c r="M9" s="3">
-        <v>200</v>
       </c>
       <c r="N9" s="3">
         <v>200</v>
@@ -910,10 +923,10 @@
         <v>200</v>
       </c>
       <c r="P9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R9" s="3">
         <v>100</v>
@@ -925,7 +938,7 @@
         <v>100</v>
       </c>
       <c r="U9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>100</v>
@@ -933,11 +946,11 @@
       <c r="W9" s="3">
         <v>200</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
+      <c r="X9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>200</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
@@ -954,62 +967,68 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
-        <v>100</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
-        <v>100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
+        <v>100</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
       <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
         <v>-100</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
       <c r="U10" s="3">
         <v>0</v>
       </c>
@@ -1019,11 +1038,11 @@
       <c r="W10" s="3">
         <v>0</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
@@ -1040,8 +1059,14 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1072,44 +1097,46 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>600</v>
+      </c>
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>300</v>
       </c>
       <c r="I12" s="3">
         <v>300</v>
       </c>
       <c r="J12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K12" s="3">
         <v>300</v>
       </c>
       <c r="L12" s="3">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3">
+        <v>300</v>
+      </c>
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1158,8 +1185,14 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1244,41 +1277,47 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1289,13 +1328,13 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
-        <v>100</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>100</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1303,35 +1342,41 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="3">
         <v>2500</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1416,8 +1461,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1445,180 +1496,194 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2400</v>
       </c>
-      <c r="AA17" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>100</v>
-      </c>
       <c r="AC17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-100</v>
       </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1649,8 +1714,10 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1697,17 +1764,17 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1732,97 +1799,109 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-400</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="3">
-        <v>0</v>
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
+      <c r="AC21" s="3">
+        <v>0</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1835,14 +1914,14 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1866,25 +1945,25 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
-        <v>100</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1892,11 +1971,11 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1907,94 +1986,106 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-800</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-600</v>
       </c>
       <c r="V23" s="3">
         <v>-500</v>
       </c>
       <c r="W23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2079,8 +2170,14 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2165,180 +2262,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-800</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-600</v>
       </c>
       <c r="V26" s="3">
         <v>-500</v>
       </c>
       <c r="W26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AC26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-800</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-600</v>
       </c>
       <c r="V27" s="3">
         <v>-500</v>
       </c>
       <c r="W27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AC27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2423,8 +2538,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2509,8 +2630,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2595,8 +2722,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2681,8 +2814,14 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2729,17 +2868,17 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2764,97 +2903,109 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-600</v>
       </c>
       <c r="V33" s="3">
         <v>-500</v>
       </c>
       <c r="W33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AC33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2939,185 +3090,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-600</v>
       </c>
       <c r="V35" s="3">
         <v>-500</v>
       </c>
       <c r="W35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AC35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3148,8 +3317,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3180,80 +3351,82 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1300</v>
+        <v>8300</v>
       </c>
       <c r="E41" s="3">
-        <v>2300</v>
+        <v>500</v>
       </c>
       <c r="F41" s="3">
         <v>1300</v>
       </c>
       <c r="G41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I41" s="3">
         <v>2000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
       <c r="R41" s="3">
         <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
       <c r="U41" s="3">
+        <v>100</v>
+      </c>
+      <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1100</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
         <v>0</v>
       </c>
@@ -3263,11 +3436,17 @@
       <c r="AC41" s="3">
         <v>0</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3352,25 +3531,31 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
@@ -3385,43 +3570,43 @@
         <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
       </c>
       <c r="O43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3435,11 +3620,17 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3462,10 +3653,10 @@
         <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L44" s="3">
         <v>100</v>
@@ -3477,13 +3668,13 @@
         <v>100</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P44" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
@@ -3497,20 +3688,20 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
       <c r="Z44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
@@ -3521,52 +3712,58 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>400</v>
       </c>
       <c r="G45" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H45" s="3">
         <v>400</v>
       </c>
       <c r="I45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J45" s="3">
         <v>400</v>
       </c>
       <c r="K45" s="3">
+        <v>500</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
+        <v>400</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -3575,10 +3772,10 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
@@ -3596,108 +3793,120 @@
         <v>100</v>
       </c>
       <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2000</v>
+        <v>8700</v>
       </c>
       <c r="E46" s="3">
-        <v>3300</v>
+        <v>1000</v>
       </c>
       <c r="F46" s="3">
         <v>2000</v>
       </c>
       <c r="G46" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I46" s="3">
         <v>2700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>100</v>
-      </c>
       <c r="R46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S46" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T46" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U46" s="3">
         <v>300</v>
       </c>
       <c r="V46" s="3">
+        <v>200</v>
+      </c>
+      <c r="W46" s="3">
+        <v>300</v>
+      </c>
+      <c r="X46" s="3">
         <v>600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1200</v>
       </c>
-      <c r="Y46" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>100</v>
-      </c>
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3782,8 +3991,14 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3791,44 +4006,44 @@
         <v>800</v>
       </c>
       <c r="E48" s="3">
+        <v>800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>800</v>
+      </c>
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1000</v>
       </c>
       <c r="M48" s="3">
         <v>1000</v>
       </c>
       <c r="N48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P48" s="3">
         <v>1100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1300</v>
       </c>
-      <c r="P48" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>100</v>
-      </c>
       <c r="R48" s="3">
         <v>100</v>
       </c>
@@ -3848,13 +4063,13 @@
         <v>100</v>
       </c>
       <c r="X48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>0</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
@@ -3868,8 +4083,14 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3880,28 +4101,28 @@
         <v>5700</v>
       </c>
       <c r="F49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="G49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H49" s="3">
         <v>5800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>5800</v>
-      </c>
-      <c r="H49" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I49" s="3">
-        <v>6200</v>
       </c>
       <c r="J49" s="3">
         <v>6200</v>
       </c>
       <c r="K49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="L49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M49" s="3">
         <v>6300</v>
-      </c>
-      <c r="L49" s="3">
-        <v>8500</v>
-      </c>
-      <c r="M49" s="3">
-        <v>8500</v>
       </c>
       <c r="N49" s="3">
         <v>8500</v>
@@ -3910,10 +4131,10 @@
         <v>8500</v>
       </c>
       <c r="P49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="Q49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="R49" s="3">
         <v>2000</v>
@@ -3922,10 +4143,10 @@
         <v>2000</v>
       </c>
       <c r="T49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="U49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="V49" s="3">
         <v>2100</v>
@@ -3933,29 +4154,35 @@
       <c r="W49" s="3">
         <v>2100</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
+      <c r="X49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>2100</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC49" s="3">
         <v>2400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2500</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4040,8 +4267,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4126,8 +4359,14 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4188,18 +4427,18 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>0</v>
       </c>
       <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1900</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4212,8 +4451,14 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4298,94 +4543,106 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F54" s="3">
         <v>8500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>9500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>15400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>10100</v>
-      </c>
-      <c r="P54" s="3">
-        <v>2200</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>2200</v>
       </c>
       <c r="R54" s="3">
         <v>2200</v>
       </c>
       <c r="S54" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T54" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U54" s="3">
         <v>2400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3100</v>
       </c>
-      <c r="Y54" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB54" s="3">
         <v>200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2500</v>
       </c>
-      <c r="AC54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4416,8 +4673,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4448,19 +4707,21 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
-      </c>
-      <c r="E57" s="3">
-        <v>500</v>
-      </c>
-      <c r="F57" s="3">
-        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>500</v>
@@ -4469,7 +4730,7 @@
         <v>500</v>
       </c>
       <c r="I57" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J57" s="3">
         <v>500</v>
@@ -4478,52 +4739,52 @@
         <v>600</v>
       </c>
       <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
+        <v>600</v>
+      </c>
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>700</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>700</v>
-      </c>
-      <c r="R57" s="3">
-        <v>800</v>
       </c>
       <c r="S57" s="3">
         <v>700</v>
       </c>
       <c r="T57" s="3">
+        <v>800</v>
+      </c>
+      <c r="U57" s="3">
+        <v>700</v>
+      </c>
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>100</v>
-      </c>
       <c r="Z57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
@@ -4531,11 +4792,17 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4546,10 +4813,10 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4564,37 +4831,37 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="O58" s="3">
         <v>1600</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="R58" s="3">
+        <v>100</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3">
-        <v>100</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4605,37 +4872,43 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H59" s="3">
         <v>200</v>
@@ -4647,7 +4920,7 @@
         <v>200</v>
       </c>
       <c r="K59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
@@ -4656,37 +4929,37 @@
         <v>100</v>
       </c>
       <c r="N59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O59" s="3">
         <v>100</v>
       </c>
       <c r="P59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
       <c r="V59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
@@ -4703,85 +4976,91 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F60" s="3">
         <v>700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>900</v>
-      </c>
-      <c r="F60" s="3">
-        <v>800</v>
-      </c>
-      <c r="G60" s="3">
-        <v>700</v>
       </c>
       <c r="H60" s="3">
         <v>800</v>
       </c>
       <c r="I60" s="3">
+        <v>700</v>
+      </c>
+      <c r="J60" s="3">
         <v>800</v>
-      </c>
-      <c r="J60" s="3">
-        <v>700</v>
       </c>
       <c r="K60" s="3">
         <v>800</v>
       </c>
       <c r="L60" s="3">
+        <v>700</v>
+      </c>
+      <c r="M60" s="3">
+        <v>800</v>
+      </c>
+      <c r="N60" s="3">
         <v>1000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>400</v>
-      </c>
-      <c r="W60" s="3">
-        <v>200</v>
-      </c>
-      <c r="X60" s="3">
-        <v>200</v>
       </c>
       <c r="Y60" s="3">
         <v>200</v>
       </c>
       <c r="Z60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB60" s="3">
         <v>0</v>
@@ -4789,26 +5068,32 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
         <v>2100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2100</v>
       </c>
-      <c r="F61" s="3">
-        <v>100</v>
-      </c>
-      <c r="G61" s="3">
-        <v>100</v>
-      </c>
       <c r="H61" s="3">
         <v>100</v>
       </c>
@@ -4825,20 +5110,20 @@
         <v>100</v>
       </c>
       <c r="M61" s="3">
+        <v>100</v>
+      </c>
+      <c r="N61" s="3">
+        <v>100</v>
+      </c>
+      <c r="O61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4878,13 +5163,19 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -4899,16 +5190,16 @@
         <v>0</v>
       </c>
       <c r="I62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3">
-        <v>100</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
+        <v>100</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -4922,11 +5213,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -4964,8 +5255,14 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5050,8 +5347,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5136,8 +5439,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5222,82 +5531,88 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F66" s="3">
         <v>2800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1000</v>
       </c>
       <c r="J66" s="3">
         <v>900</v>
       </c>
       <c r="K66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L66" s="3">
         <v>900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
+        <v>900</v>
+      </c>
+      <c r="N66" s="3">
         <v>1100</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2800</v>
-      </c>
-      <c r="N66" s="3">
-        <v>2800</v>
       </c>
       <c r="O66" s="3">
         <v>2800</v>
       </c>
       <c r="P66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R66" s="3">
         <v>900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>400</v>
-      </c>
-      <c r="W66" s="3">
-        <v>200</v>
-      </c>
-      <c r="X66" s="3">
-        <v>200</v>
       </c>
       <c r="Y66" s="3">
         <v>200</v>
       </c>
       <c r="Z66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB66" s="3">
         <v>0</v>
@@ -5305,11 +5620,17 @@
       <c r="AC66" s="3">
         <v>0</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5340,8 +5661,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5426,8 +5749,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5512,8 +5841,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5598,8 +5933,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5684,94 +6025,106 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-26100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-24300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-23500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-22500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-20800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-19700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-18700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-18000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-14200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-12700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-11800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-9600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-9300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-8900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-8000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-7200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-6800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-6200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-5700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5856,8 +6209,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5942,8 +6301,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6028,94 +6393,106 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F76" s="3">
         <v>5700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>11900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>14300</v>
-      </c>
-      <c r="M76" s="3">
-        <v>7300</v>
-      </c>
-      <c r="N76" s="3">
-        <v>7100</v>
       </c>
       <c r="O76" s="3">
         <v>7300</v>
       </c>
       <c r="P76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>7300</v>
+      </c>
+      <c r="R76" s="3">
         <v>1300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2900</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>100</v>
-      </c>
       <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC76" s="3">
         <v>2400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>2500</v>
       </c>
-      <c r="AC76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6200,185 +6577,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-600</v>
       </c>
       <c r="V81" s="3">
         <v>-500</v>
       </c>
       <c r="W81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AC81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6409,8 +6804,10 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6435,24 +6832,24 @@
       <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>-100</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -6472,31 +6869,37 @@
         <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>100</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>100</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
+      <c r="AC83" s="3">
+        <v>100</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6581,8 +6984,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6667,8 +7076,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6753,8 +7168,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6839,8 +7260,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6925,80 +7352,86 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
-        <v>100</v>
-      </c>
       <c r="P89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="R89" s="3">
         <v>-100</v>
       </c>
       <c r="S89" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="T89" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="U89" s="3">
         <v>-300</v>
       </c>
       <c r="V89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
         <v>0</v>
       </c>
@@ -7008,11 +7441,17 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7043,8 +7482,10 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7078,11 +7519,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -7096,11 +7537,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -7129,8 +7570,14 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7215,8 +7662,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7301,8 +7754,14 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7327,32 +7786,32 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -7364,14 +7823,14 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -7384,11 +7843,17 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7419,8 +7884,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7505,8 +7972,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7591,8 +8064,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7677,8 +8156,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7763,80 +8248,86 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>100</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>100</v>
+      </c>
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
-        <v>100</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1500</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -7846,11 +8337,17 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7932,83 +8429,89 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
-        <v>200</v>
-      </c>
-      <c r="N102" s="3">
-        <v>100</v>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O102" s="3">
         <v>200</v>
       </c>
       <c r="P102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>100</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
+        <v>100</v>
+      </c>
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
@@ -8018,7 +8521,13 @@
       <c r="AC102" s="3">
         <v>0</v>
       </c>
-      <c r="AD102" s="3" t="s">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>NTRB</t>
   </si>
@@ -656,141 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -798,25 +802,25 @@
         <v>400</v>
       </c>
       <c r="E8" s="3">
+        <v>400</v>
+      </c>
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>700</v>
-      </c>
-      <c r="H8" s="3">
-        <v>500</v>
       </c>
       <c r="I8" s="3">
         <v>500</v>
       </c>
       <c r="J8" s="3">
+        <v>500</v>
+      </c>
+      <c r="K8" s="3">
         <v>600</v>
-      </c>
-      <c r="K8" s="3">
-        <v>500</v>
       </c>
       <c r="L8" s="3">
         <v>500</v>
@@ -825,44 +829,44 @@
         <v>500</v>
       </c>
       <c r="N8" s="3">
+        <v>500</v>
+      </c>
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
-      </c>
-      <c r="P8" s="3">
-        <v>400</v>
       </c>
       <c r="Q8" s="3">
         <v>400</v>
       </c>
       <c r="R8" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="S8" s="3">
         <v>100</v>
       </c>
       <c r="T8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
       </c>
       <c r="W8" s="3">
+        <v>100</v>
+      </c>
+      <c r="X8" s="3">
         <v>200</v>
       </c>
-      <c r="X8" s="3">
-        <v>100</v>
-      </c>
       <c r="Y8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="3">
         <v>200</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
@@ -878,34 +882,37 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
         <v>200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>300</v>
       </c>
       <c r="F9" s="3">
         <v>300</v>
       </c>
       <c r="G9" s="3">
+        <v>300</v>
+      </c>
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>300</v>
       </c>
       <c r="K9" s="3">
         <v>300</v>
@@ -914,10 +921,10 @@
         <v>300</v>
       </c>
       <c r="M9" s="3">
+        <v>300</v>
+      </c>
+      <c r="N9" s="3">
         <v>400</v>
-      </c>
-      <c r="N9" s="3">
-        <v>200</v>
       </c>
       <c r="O9" s="3">
         <v>200</v>
@@ -929,7 +936,7 @@
         <v>200</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S9" s="3">
         <v>100</v>
@@ -944,17 +951,17 @@
         <v>100</v>
       </c>
       <c r="W9" s="3">
+        <v>100</v>
+      </c>
+      <c r="X9" s="3">
         <v>200</v>
       </c>
-      <c r="X9" s="3">
-        <v>100</v>
-      </c>
       <c r="Y9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z9" s="3">
         <v>200</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,65 +980,68 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
-        <v>100</v>
-      </c>
       <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
         <v>300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>200</v>
       </c>
       <c r="L10" s="3">
         <v>200</v>
       </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
         <v>200</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
       <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>-100</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
         <v>0</v>
       </c>
@@ -1044,8 +1054,8 @@
       <c r="Y10" s="3">
         <v>0</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
+      <c r="Z10" s="3">
+        <v>0</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
@@ -1065,8 +1075,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1099,28 +1112,29 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>600</v>
       </c>
       <c r="F12" s="3">
         <v>600</v>
       </c>
       <c r="G12" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H12" s="3">
         <v>400</v>
       </c>
       <c r="I12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J12" s="3">
         <v>300</v>
@@ -1129,17 +1143,17 @@
         <v>300</v>
       </c>
       <c r="L12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M12" s="3">
+        <v>100</v>
+      </c>
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,8 +1205,11 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,32 +1300,35 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1316,11 +1336,11 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>2200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1334,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
-        <v>100</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>100</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1348,11 +1368,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1360,12 +1380,12 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2500</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1375,8 +1395,11 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,8 +1490,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1524,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1500</v>
       </c>
       <c r="H17" s="3">
         <v>1500</v>
       </c>
       <c r="I17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J17" s="3">
         <v>2200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
-      </c>
-      <c r="O17" s="3">
-        <v>700</v>
       </c>
       <c r="P17" s="3">
         <v>700</v>
       </c>
       <c r="Q17" s="3">
+        <v>700</v>
+      </c>
+      <c r="R17" s="3">
         <v>400</v>
-      </c>
-      <c r="R17" s="3">
-        <v>300</v>
       </c>
       <c r="S17" s="3">
         <v>300</v>
       </c>
       <c r="T17" s="3">
+        <v>300</v>
+      </c>
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2400</v>
       </c>
-      <c r="AC17" s="3">
-        <v>100</v>
-      </c>
       <c r="AD17" s="3">
         <v>100</v>
       </c>
       <c r="AE17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1900</v>
+        <v>-1800</v>
       </c>
       <c r="E18" s="3">
         <v>-1900</v>
       </c>
       <c r="F18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
         <v>-200</v>
       </c>
       <c r="T18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U18" s="3">
         <v>-600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-600</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-500</v>
       </c>
       <c r="Y18" s="3">
         <v>-500</v>
       </c>
       <c r="Z18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-100</v>
       </c>
       <c r="AD18" s="3">
         <v>-100</v>
       </c>
       <c r="AE18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,13 +1749,14 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1770,14 +1804,14 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1805,94 +1839,97 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1800</v>
+        <v>-1600</v>
       </c>
       <c r="E21" s="3">
         <v>-1800</v>
       </c>
       <c r="F21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1000</v>
       </c>
       <c r="K21" s="3">
         <v>-1000</v>
       </c>
       <c r="L21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-400</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
         <v>-200</v>
       </c>
       <c r="T21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-400</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>0</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
@@ -1900,8 +1937,11 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1920,11 +1960,11 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1951,13 +1991,13 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
-        <v>100</v>
-      </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1965,8 +2005,8 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1977,8 +2017,8 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1992,100 +2032,106 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="E23" s="3">
         <v>-1900</v>
       </c>
       <c r="F23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-500</v>
       </c>
       <c r="Y23" s="3">
         <v>-500</v>
       </c>
       <c r="Z23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-100</v>
       </c>
       <c r="AD23" s="3">
         <v>-100</v>
       </c>
       <c r="AE23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2176,8 +2222,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2317,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="E26" s="3">
         <v>-1900</v>
       </c>
       <c r="F26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-500</v>
       </c>
       <c r="Y26" s="3">
         <v>-500</v>
       </c>
       <c r="Z26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-100</v>
       </c>
       <c r="AD26" s="3">
         <v>-100</v>
       </c>
       <c r="AE26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="E27" s="3">
         <v>-1900</v>
       </c>
       <c r="F27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-600</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-500</v>
       </c>
       <c r="Y27" s="3">
         <v>-500</v>
       </c>
       <c r="Z27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-100</v>
       </c>
       <c r="AD27" s="3">
         <v>-100</v>
       </c>
       <c r="AE27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2602,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2636,8 +2697,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2792,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,13 +2887,16 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2874,14 +2944,14 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2909,103 +2979,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="E33" s="3">
         <v>-1900</v>
       </c>
       <c r="F33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-500</v>
       </c>
       <c r="Y33" s="3">
         <v>-500</v>
       </c>
       <c r="Z33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-100</v>
       </c>
       <c r="AD33" s="3">
         <v>-100</v>
       </c>
       <c r="AE33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3172,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="E35" s="3">
         <v>-1900</v>
       </c>
       <c r="F35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-500</v>
       </c>
       <c r="Y35" s="3">
         <v>-500</v>
       </c>
       <c r="Z35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-100</v>
       </c>
       <c r="AD35" s="3">
         <v>-100</v>
       </c>
       <c r="AE35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3404,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,55 +3439,56 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E41" s="3">
         <v>8300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
-      </c>
-      <c r="P41" s="3">
-        <v>200</v>
       </c>
       <c r="Q41" s="3">
         <v>200</v>
       </c>
       <c r="R41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S41" s="3">
         <v>0</v>
@@ -3410,26 +3497,26 @@
         <v>0</v>
       </c>
       <c r="U41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1100</v>
       </c>
-      <c r="AA41" s="3">
-        <v>0</v>
-      </c>
       <c r="AB41" s="3">
         <v>0</v>
       </c>
@@ -3442,11 +3529,14 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,8 +3627,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3549,7 +3642,7 @@
         <v>100</v>
       </c>
       <c r="F43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
@@ -3558,7 +3651,7 @@
         <v>200</v>
       </c>
       <c r="I43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -3576,16 +3669,16 @@
         <v>100</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
         <v>100</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -3594,22 +3687,22 @@
         <v>0</v>
       </c>
       <c r="U43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
       </c>
       <c r="W43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3626,11 +3719,14 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3659,7 +3755,7 @@
         <v>200</v>
       </c>
       <c r="L44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M44" s="3">
         <v>100</v>
@@ -3674,10 +3770,10 @@
         <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
@@ -3694,17 +3790,17 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
       <c r="Z44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
@@ -3718,28 +3814,31 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
@@ -3748,25 +3847,25 @@
         <v>400</v>
       </c>
       <c r="K45" s="3">
+        <v>400</v>
+      </c>
+      <c r="L45" s="3">
         <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>400</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
       </c>
       <c r="N45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3778,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -3799,114 +3898,120 @@
         <v>100</v>
       </c>
       <c r="AB45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
       <c r="AD45" s="3">
         <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E46" s="3">
         <v>8700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>600</v>
-      </c>
-      <c r="P46" s="3">
-        <v>300</v>
       </c>
       <c r="Q46" s="3">
         <v>300</v>
       </c>
       <c r="R46" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S46" s="3">
         <v>100</v>
       </c>
       <c r="T46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U46" s="3">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3">
         <v>300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1200</v>
       </c>
-      <c r="AA46" s="3">
-        <v>100</v>
-      </c>
       <c r="AB46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC46" s="3">
         <v>200</v>
       </c>
-      <c r="AC46" s="3">
-        <v>0</v>
-      </c>
       <c r="AD46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3997,8 +4102,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4012,25 +4120,25 @@
         <v>800</v>
       </c>
       <c r="G48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H48" s="3">
         <v>900</v>
       </c>
       <c r="I48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="J48" s="3">
         <v>1000</v>
       </c>
       <c r="K48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="L48" s="3">
         <v>1100</v>
       </c>
       <c r="M48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="N48" s="3">
         <v>1000</v>
@@ -4039,14 +4147,14 @@
         <v>1000</v>
       </c>
       <c r="P48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1300</v>
       </c>
-      <c r="R48" s="3">
-        <v>100</v>
-      </c>
       <c r="S48" s="3">
         <v>100</v>
       </c>
@@ -4069,10 +4177,10 @@
         <v>100</v>
       </c>
       <c r="Z48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
@@ -4089,13 +4197,16 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="E49" s="3">
         <v>5700</v>
@@ -4107,13 +4218,13 @@
         <v>5700</v>
       </c>
       <c r="H49" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="3">
         <v>5800</v>
       </c>
       <c r="J49" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="K49" s="3">
         <v>6200</v>
@@ -4122,10 +4233,10 @@
         <v>6200</v>
       </c>
       <c r="M49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="N49" s="3">
         <v>6300</v>
-      </c>
-      <c r="N49" s="3">
-        <v>8500</v>
       </c>
       <c r="O49" s="3">
         <v>8500</v>
@@ -4137,7 +4248,7 @@
         <v>8500</v>
       </c>
       <c r="R49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="S49" s="3">
         <v>2000</v>
@@ -4149,7 +4260,7 @@
         <v>2000</v>
       </c>
       <c r="V49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="W49" s="3">
         <v>2100</v>
@@ -4160,8 +4271,8 @@
       <c r="Y49" s="3">
         <v>2100</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
+      <c r="Z49" s="3">
+        <v>2100</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
@@ -4169,20 +4280,23 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD49" s="3">
         <v>2400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2500</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4387,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,8 +4482,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4433,15 +4553,15 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1900</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4457,8 +4577,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,55 +4672,58 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E54" s="3">
         <v>15200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10100</v>
-      </c>
-      <c r="R54" s="3">
-        <v>2200</v>
       </c>
       <c r="S54" s="3">
         <v>2200</v>
@@ -4606,43 +4732,46 @@
         <v>2200</v>
       </c>
       <c r="U54" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="V54" s="3">
         <v>2400</v>
       </c>
       <c r="W54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X54" s="3">
         <v>2500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3100</v>
       </c>
-      <c r="AA54" s="3">
-        <v>100</v>
-      </c>
       <c r="AB54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC54" s="3">
         <v>200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2500</v>
       </c>
-      <c r="AE54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4804,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,22 +4839,23 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
       </c>
       <c r="H57" s="3">
         <v>500</v>
@@ -4736,58 +4867,58 @@
         <v>500</v>
       </c>
       <c r="K57" s="3">
+        <v>500</v>
+      </c>
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>600</v>
       </c>
       <c r="N57" s="3">
         <v>600</v>
       </c>
       <c r="O57" s="3">
+        <v>600</v>
+      </c>
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
-      </c>
-      <c r="R57" s="3">
-        <v>700</v>
       </c>
       <c r="S57" s="3">
         <v>700</v>
       </c>
       <c r="T57" s="3">
+        <v>700</v>
+      </c>
+      <c r="U57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3">
-        <v>100</v>
-      </c>
       <c r="AA57" s="3">
         <v>100</v>
       </c>
       <c r="AB57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
@@ -4798,11 +4929,14 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4819,7 +4953,7 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -4837,34 +4971,34 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>100</v>
+      </c>
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1600</v>
       </c>
-      <c r="R58" s="3">
-        <v>100</v>
-      </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3">
-        <v>100</v>
-      </c>
       <c r="W58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4878,40 +5012,43 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
+      <c r="AB58" s="3">
+        <v>0</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>200</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
       </c>
       <c r="G59" s="3">
+        <v>200</v>
+      </c>
+      <c r="H59" s="3">
         <v>300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>200</v>
@@ -4926,14 +5063,14 @@
         <v>200</v>
       </c>
       <c r="M59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N59" s="3">
+        <v>100</v>
+      </c>
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
-        <v>100</v>
-      </c>
       <c r="P59" s="3">
         <v>100</v>
       </c>
@@ -4941,28 +5078,28 @@
         <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
       </c>
       <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>500</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
       <c r="W59" s="3">
         <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4982,79 +5119,82 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>800</v>
       </c>
       <c r="K60" s="3">
         <v>800</v>
       </c>
       <c r="L60" s="3">
+        <v>800</v>
+      </c>
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
-      </c>
-      <c r="P60" s="3">
-        <v>2600</v>
       </c>
       <c r="Q60" s="3">
         <v>2600</v>
       </c>
       <c r="R60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S60" s="3">
         <v>900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
-      </c>
-      <c r="W60" s="3">
-        <v>400</v>
       </c>
       <c r="X60" s="3">
         <v>400</v>
       </c>
       <c r="Y60" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Z60" s="3">
         <v>200</v>
@@ -5063,7 +5203,7 @@
         <v>200</v>
       </c>
       <c r="AB60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC60" s="3">
         <v>0</v>
@@ -5074,28 +5214,31 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
-        <v>100</v>
-      </c>
       <c r="F61" s="3">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>2100</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
@@ -5116,17 +5259,17 @@
         <v>100</v>
       </c>
       <c r="O61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P61" s="3">
         <v>200</v>
       </c>
       <c r="Q61" s="3">
+        <v>200</v>
+      </c>
+      <c r="R61" s="3">
         <v>300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -5169,16 +5312,19 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -5196,13 +5342,13 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>100</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -5219,8 +5365,8 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -5261,8 +5407,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5502,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5597,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,46 +5692,49 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>900</v>
       </c>
       <c r="J66" s="3">
         <v>900</v>
       </c>
       <c r="K66" s="3">
+        <v>900</v>
+      </c>
+      <c r="L66" s="3">
         <v>1000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>900</v>
       </c>
       <c r="M66" s="3">
         <v>900</v>
       </c>
       <c r="N66" s="3">
+        <v>900</v>
+      </c>
+      <c r="O66" s="3">
         <v>1100</v>
-      </c>
-      <c r="O66" s="3">
-        <v>2800</v>
       </c>
       <c r="P66" s="3">
         <v>2800</v>
@@ -5585,28 +5743,28 @@
         <v>2800</v>
       </c>
       <c r="R66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S66" s="3">
         <v>900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
-      </c>
-      <c r="W66" s="3">
-        <v>400</v>
       </c>
       <c r="X66" s="3">
         <v>400</v>
       </c>
       <c r="Y66" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Z66" s="3">
         <v>200</v>
@@ -5615,7 +5773,7 @@
         <v>200</v>
       </c>
       <c r="AB66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC66" s="3">
         <v>0</v>
@@ -5626,11 +5784,14 @@
       <c r="AE66" s="3">
         <v>0</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5824,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5917,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6012,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6107,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6202,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-29900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-28000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-26100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-24300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-23500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-22500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-20800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-19700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-18700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-18000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-14200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-9600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-9500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-8000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-200</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6392,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6487,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +6582,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E76" s="3">
         <v>13400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2100</v>
-      </c>
-      <c r="X76" s="3">
-        <v>2400</v>
       </c>
       <c r="Y76" s="3">
         <v>2400</v>
       </c>
       <c r="Z76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA76" s="3">
         <v>2900</v>
       </c>
-      <c r="AA76" s="3">
-        <v>0</v>
-      </c>
       <c r="AB76" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD76" s="3">
         <v>2400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2500</v>
       </c>
-      <c r="AE76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6772,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="E81" s="3">
         <v>-1900</v>
       </c>
       <c r="F81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-500</v>
       </c>
       <c r="Y81" s="3">
         <v>-500</v>
       </c>
       <c r="Z81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-100</v>
       </c>
       <c r="AD81" s="3">
         <v>-100</v>
       </c>
       <c r="AE81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,8 +7004,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6838,21 +7037,21 @@
       <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>100</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-100</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -6875,10 +7074,10 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>100</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
@@ -6886,11 +7085,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>100</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
@@ -6898,8 +7097,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7192,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7287,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7382,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7477,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,82 +7572,85 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
+        <v>100</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-300</v>
       </c>
       <c r="X89" s="3">
         <v>-300</v>
       </c>
       <c r="Y89" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="Z89" s="3">
         <v>-400</v>
       </c>
       <c r="AA89" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -7447,11 +7664,14 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,8 +7704,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7525,8 +7746,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -7543,8 +7764,8 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7576,8 +7797,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7892,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,8 +7987,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7792,29 +8022,29 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -7829,11 +8059,11 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
@@ -7849,11 +8079,14 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8119,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7978,8 +8212,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8307,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8402,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,26 +8497,29 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>8700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>2100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -8281,56 +8527,56 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>100</v>
+      </c>
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
-        <v>100</v>
-      </c>
       <c r="W100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1500</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -8343,11 +8589,14 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8435,86 +8684,89 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>7900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
-        <v>100</v>
-      </c>
       <c r="Q102" s="3">
+        <v>100</v>
+      </c>
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
-        <v>100</v>
-      </c>
       <c r="V102" s="3">
+        <v>100</v>
+      </c>
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
         <v>0</v>
       </c>
@@ -8527,7 +8779,10 @@
       <c r="AE102" s="3">
         <v>0</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>NTRB</t>
   </si>
@@ -656,174 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E8" s="3">
         <v>400</v>
       </c>
       <c r="F8" s="3">
+        <v>400</v>
+      </c>
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>700</v>
-      </c>
-      <c r="I8" s="3">
-        <v>500</v>
       </c>
       <c r="J8" s="3">
         <v>500</v>
       </c>
       <c r="K8" s="3">
+        <v>500</v>
+      </c>
+      <c r="L8" s="3">
         <v>600</v>
-      </c>
-      <c r="L8" s="3">
-        <v>500</v>
       </c>
       <c r="M8" s="3">
         <v>500</v>
@@ -832,44 +836,44 @@
         <v>500</v>
       </c>
       <c r="O8" s="3">
+        <v>500</v>
+      </c>
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>400</v>
       </c>
       <c r="R8" s="3">
         <v>400</v>
       </c>
       <c r="S8" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="T8" s="3">
         <v>100</v>
       </c>
       <c r="U8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>100</v>
       </c>
       <c r="X8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>200</v>
       </c>
-      <c r="Y8" s="3">
-        <v>100</v>
-      </c>
       <c r="Z8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
@@ -885,37 +889,40 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
         <v>300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>300</v>
       </c>
       <c r="G9" s="3">
         <v>300</v>
       </c>
       <c r="H9" s="3">
+        <v>300</v>
+      </c>
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
-      </c>
-      <c r="K9" s="3">
-        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>300</v>
@@ -924,10 +931,10 @@
         <v>300</v>
       </c>
       <c r="N9" s="3">
+        <v>300</v>
+      </c>
+      <c r="O9" s="3">
         <v>400</v>
-      </c>
-      <c r="O9" s="3">
-        <v>200</v>
       </c>
       <c r="P9" s="3">
         <v>200</v>
@@ -939,7 +946,7 @@
         <v>200</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T9" s="3">
         <v>100</v>
@@ -954,17 +961,17 @@
         <v>100</v>
       </c>
       <c r="X9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="3">
         <v>200</v>
       </c>
-      <c r="Y9" s="3">
-        <v>100</v>
-      </c>
       <c r="Z9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA9" s="3">
         <v>200</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
@@ -983,68 +990,71 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3">
+        <v>200</v>
+      </c>
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
-        <v>100</v>
-      </c>
       <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
         <v>300</v>
-      </c>
-      <c r="L10" s="3">
-        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>200</v>
       </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O10" s="3">
         <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
       </c>
       <c r="S10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T10" s="3">
         <v>0</v>
       </c>
       <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>-100</v>
       </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
       <c r="W10" s="3">
         <v>0</v>
       </c>
@@ -1057,8 +1067,8 @@
       <c r="Z10" s="3">
         <v>0</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
+      <c r="AA10" s="3">
+        <v>0</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
@@ -1078,8 +1088,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1113,31 +1126,32 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
         <v>800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>600</v>
       </c>
       <c r="G12" s="3">
         <v>600</v>
       </c>
       <c r="H12" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I12" s="3">
         <v>400</v>
       </c>
       <c r="J12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K12" s="3">
         <v>300</v>
@@ -1146,17 +1160,17 @@
         <v>300</v>
       </c>
       <c r="M12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N12" s="3">
+        <v>100</v>
+      </c>
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1208,8 +1222,11 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1303,35 +1320,38 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1339,11 +1359,11 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1357,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
-        <v>100</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>100</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1371,11 +1391,11 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
@@ -1383,12 +1403,12 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3">
         <v>2500</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1398,31 +1418,34 @@
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1493,8 +1516,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1525,198 +1551,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H17" s="3">
         <v>2200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1500</v>
       </c>
       <c r="I17" s="3">
         <v>1500</v>
       </c>
       <c r="J17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1800</v>
-      </c>
-      <c r="P17" s="3">
-        <v>700</v>
       </c>
       <c r="Q17" s="3">
         <v>700</v>
       </c>
       <c r="R17" s="3">
+        <v>700</v>
+      </c>
+      <c r="S17" s="3">
         <v>400</v>
-      </c>
-      <c r="S17" s="3">
-        <v>300</v>
       </c>
       <c r="T17" s="3">
         <v>300</v>
       </c>
       <c r="U17" s="3">
+        <v>300</v>
+      </c>
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2400</v>
       </c>
-      <c r="AD17" s="3">
-        <v>100</v>
-      </c>
       <c r="AE17" s="3">
         <v>100</v>
       </c>
       <c r="AF17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1800</v>
+        <v>-1400</v>
       </c>
       <c r="E18" s="3">
-        <v>-1900</v>
+        <v>-1400</v>
       </c>
       <c r="F18" s="3">
         <v>-1900</v>
       </c>
       <c r="G18" s="3">
-        <v>-1800</v>
+        <v>-1300</v>
       </c>
       <c r="H18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="T18" s="3">
         <v>-200</v>
       </c>
       <c r="U18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V18" s="3">
         <v>-600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-500</v>
       </c>
       <c r="Z18" s="3">
         <v>-500</v>
       </c>
       <c r="AA18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-100</v>
       </c>
       <c r="AE18" s="3">
         <v>-100</v>
       </c>
       <c r="AF18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1750,31 +1783,32 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1807,14 +1841,14 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1842,97 +1876,100 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1600</v>
+        <v>-1400</v>
       </c>
       <c r="E21" s="3">
-        <v>-1800</v>
+        <v>-1300</v>
       </c>
       <c r="F21" s="3">
         <v>-1800</v>
       </c>
       <c r="G21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1000</v>
       </c>
       <c r="L21" s="3">
         <v>-1000</v>
       </c>
       <c r="M21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N21" s="3">
         <v>-600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="T21" s="3">
         <v>-200</v>
       </c>
       <c r="U21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V21" s="3">
         <v>-900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>0</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
@@ -1940,8 +1977,11 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1963,11 +2003,11 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1994,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
-        <v>100</v>
-      </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2008,8 +2048,8 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -2020,8 +2060,8 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2035,126 +2075,132 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-1900</v>
       </c>
       <c r="F23" s="3">
         <v>-1900</v>
       </c>
       <c r="G23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-500</v>
       </c>
       <c r="Z23" s="3">
         <v>-500</v>
       </c>
       <c r="AA23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-100</v>
       </c>
       <c r="AE23" s="3">
         <v>-100</v>
       </c>
       <c r="AF23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2225,8 +2271,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2320,198 +2369,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-1900</v>
       </c>
       <c r="F26" s="3">
         <v>-1900</v>
       </c>
       <c r="G26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-300</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-500</v>
       </c>
       <c r="Z26" s="3">
         <v>-500</v>
       </c>
       <c r="AA26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-100</v>
       </c>
       <c r="AE26" s="3">
         <v>-100</v>
       </c>
       <c r="AF26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-1900</v>
       </c>
       <c r="F27" s="3">
         <v>-1900</v>
       </c>
       <c r="G27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-500</v>
       </c>
       <c r="Z27" s="3">
         <v>-500</v>
       </c>
       <c r="AA27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-100</v>
       </c>
       <c r="AE27" s="3">
         <v>-100</v>
       </c>
       <c r="AF27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2605,8 +2663,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2700,8 +2761,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2795,8 +2859,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2890,31 +2957,34 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2947,14 +3017,14 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2982,106 +3052,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-1900</v>
       </c>
       <c r="F33" s="3">
         <v>-1900</v>
       </c>
       <c r="G33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-300</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-500</v>
       </c>
       <c r="Z33" s="3">
         <v>-500</v>
       </c>
       <c r="AA33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-100</v>
       </c>
       <c r="AE33" s="3">
         <v>-100</v>
       </c>
       <c r="AF33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3175,203 +3251,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-1900</v>
       </c>
       <c r="F35" s="3">
         <v>-1900</v>
       </c>
       <c r="G35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-300</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-500</v>
       </c>
       <c r="Z35" s="3">
         <v>-500</v>
       </c>
       <c r="AA35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-100</v>
       </c>
       <c r="AE35" s="3">
         <v>-100</v>
       </c>
       <c r="AF35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3405,8 +3490,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3440,58 +3526,59 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>200</v>
       </c>
       <c r="R41" s="3">
         <v>200</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -3500,26 +3587,26 @@
         <v>0</v>
       </c>
       <c r="V41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1100</v>
       </c>
-      <c r="AB41" s="3">
-        <v>0</v>
-      </c>
       <c r="AC41" s="3">
         <v>0</v>
       </c>
@@ -3532,11 +3619,14 @@
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3630,8 +3720,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3645,7 +3738,7 @@
         <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
@@ -3654,7 +3747,7 @@
         <v>200</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -3672,16 +3765,16 @@
         <v>100</v>
       </c>
       <c r="P43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R43" s="3">
         <v>100</v>
       </c>
       <c r="S43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3690,22 +3783,22 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W43" s="3">
         <v>100</v>
       </c>
       <c r="X43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
       <c r="Z43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -3722,11 +3815,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3758,7 +3854,7 @@
         <v>200</v>
       </c>
       <c r="M44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N44" s="3">
         <v>100</v>
@@ -3773,10 +3869,10 @@
         <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
@@ -3793,17 +3889,17 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
       <c r="AA44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
@@ -3817,58 +3913,61 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
       </c>
       <c r="L45" s="3">
+        <v>400</v>
+      </c>
+      <c r="M45" s="3">
         <v>500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>400</v>
       </c>
       <c r="N45" s="3">
         <v>400</v>
       </c>
       <c r="O45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3">
+        <v>200</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
@@ -3880,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>100</v>
@@ -3901,140 +4000,146 @@
         <v>100</v>
       </c>
       <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E46" s="3">
         <v>7200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>600</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>300</v>
       </c>
       <c r="R46" s="3">
         <v>300</v>
       </c>
       <c r="S46" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="T46" s="3">
         <v>100</v>
       </c>
       <c r="U46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
         <v>300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1200</v>
       </c>
-      <c r="AB46" s="3">
-        <v>100</v>
-      </c>
       <c r="AC46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD46" s="3">
         <v>200</v>
       </c>
-      <c r="AD46" s="3">
-        <v>0</v>
-      </c>
       <c r="AE46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4105,13 +4210,16 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E48" s="3">
         <v>800</v>
@@ -4123,25 +4231,25 @@
         <v>800</v>
       </c>
       <c r="H48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I48" s="3">
         <v>900</v>
       </c>
       <c r="J48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="K48" s="3">
         <v>1000</v>
       </c>
       <c r="L48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="M48" s="3">
         <v>1100</v>
       </c>
       <c r="N48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="O48" s="3">
         <v>1000</v>
@@ -4150,14 +4258,14 @@
         <v>1000</v>
       </c>
       <c r="Q48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R48" s="3">
         <v>1100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1300</v>
       </c>
-      <c r="S48" s="3">
-        <v>100</v>
-      </c>
       <c r="T48" s="3">
         <v>100</v>
       </c>
@@ -4180,10 +4288,10 @@
         <v>100</v>
       </c>
       <c r="AA48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>0</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -4200,8 +4308,11 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4209,7 +4320,7 @@
         <v>5600</v>
       </c>
       <c r="E49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="F49" s="3">
         <v>5700</v>
@@ -4221,13 +4332,13 @@
         <v>5700</v>
       </c>
       <c r="I49" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="J49" s="3">
         <v>5800</v>
       </c>
       <c r="K49" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="L49" s="3">
         <v>6200</v>
@@ -4236,10 +4347,10 @@
         <v>6200</v>
       </c>
       <c r="N49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="O49" s="3">
         <v>6300</v>
-      </c>
-      <c r="O49" s="3">
-        <v>8500</v>
       </c>
       <c r="P49" s="3">
         <v>8500</v>
@@ -4251,7 +4362,7 @@
         <v>8500</v>
       </c>
       <c r="S49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="T49" s="3">
         <v>2000</v>
@@ -4263,7 +4374,7 @@
         <v>2000</v>
       </c>
       <c r="W49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="X49" s="3">
         <v>2100</v>
@@ -4274,8 +4385,8 @@
       <c r="Z49" s="3">
         <v>2100</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
+      <c r="AA49" s="3">
+        <v>2100</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
@@ -4283,20 +4394,23 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE49" s="3">
         <v>2400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2500</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4390,8 +4504,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4485,31 +4602,34 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4556,15 +4676,15 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1900</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4580,8 +4700,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4675,58 +4798,61 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E54" s="3">
         <v>13600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10100</v>
-      </c>
-      <c r="S54" s="3">
-        <v>2200</v>
       </c>
       <c r="T54" s="3">
         <v>2200</v>
@@ -4735,43 +4861,46 @@
         <v>2200</v>
       </c>
       <c r="V54" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="W54" s="3">
         <v>2400</v>
       </c>
       <c r="X54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y54" s="3">
         <v>2500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3100</v>
       </c>
-      <c r="AB54" s="3">
-        <v>100</v>
-      </c>
       <c r="AC54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD54" s="3">
         <v>200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2500</v>
       </c>
-      <c r="AF54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4805,8 +4934,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4840,25 +4970,26 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>500</v>
       </c>
       <c r="I57" s="3">
         <v>500</v>
@@ -4870,58 +5001,58 @@
         <v>500</v>
       </c>
       <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
-      </c>
-      <c r="N57" s="3">
-        <v>600</v>
       </c>
       <c r="O57" s="3">
         <v>600</v>
       </c>
       <c r="P57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
-      </c>
-      <c r="S57" s="3">
-        <v>700</v>
       </c>
       <c r="T57" s="3">
         <v>700</v>
       </c>
       <c r="U57" s="3">
+        <v>700</v>
+      </c>
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
-        <v>100</v>
-      </c>
       <c r="AB57" s="3">
         <v>100</v>
       </c>
       <c r="AC57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
@@ -4932,11 +5063,14 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4947,19 +5081,19 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4974,34 +5108,34 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1600</v>
       </c>
-      <c r="S58" s="3">
-        <v>100</v>
-      </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3">
-        <v>100</v>
-      </c>
       <c r="X58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5015,23 +5149,26 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
+      <c r="AC58" s="3">
+        <v>0</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5039,16 +5176,16 @@
         <v>200</v>
       </c>
       <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>200</v>
       </c>
       <c r="G59" s="3">
         <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>200</v>
@@ -5066,14 +5203,14 @@
         <v>200</v>
       </c>
       <c r="N59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O59" s="3">
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
-        <v>100</v>
-      </c>
       <c r="Q59" s="3">
         <v>100</v>
       </c>
@@ -5081,28 +5218,28 @@
         <v>100</v>
       </c>
       <c r="S59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
       </c>
       <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
       <c r="Y59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -5122,82 +5259,85 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
-      </c>
-      <c r="K60" s="3">
-        <v>800</v>
       </c>
       <c r="L60" s="3">
         <v>800</v>
       </c>
       <c r="M60" s="3">
+        <v>800</v>
+      </c>
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>2600</v>
       </c>
       <c r="R60" s="3">
         <v>2600</v>
       </c>
       <c r="S60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="T60" s="3">
         <v>900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>700</v>
-      </c>
-      <c r="X60" s="3">
-        <v>400</v>
       </c>
       <c r="Y60" s="3">
         <v>400</v>
       </c>
       <c r="Z60" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AA60" s="3">
         <v>200</v>
@@ -5206,7 +5346,7 @@
         <v>200</v>
       </c>
       <c r="AC60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD60" s="3">
         <v>0</v>
@@ -5217,11 +5357,14 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5229,22 +5372,22 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
-        <v>100</v>
-      </c>
       <c r="G61" s="3">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>2100</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="J61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
@@ -5262,17 +5405,17 @@
         <v>100</v>
       </c>
       <c r="P61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
         <v>200</v>
       </c>
       <c r="R61" s="3">
+        <v>200</v>
+      </c>
+      <c r="S61" s="3">
         <v>300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5315,8 +5458,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5326,32 +5472,32 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>100</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -5368,8 +5514,8 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -5410,8 +5556,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5505,8 +5654,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5600,8 +5752,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5695,49 +5850,52 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>900</v>
       </c>
       <c r="K66" s="3">
         <v>900</v>
       </c>
       <c r="L66" s="3">
+        <v>900</v>
+      </c>
+      <c r="M66" s="3">
         <v>1000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>900</v>
       </c>
       <c r="N66" s="3">
         <v>900</v>
       </c>
       <c r="O66" s="3">
+        <v>900</v>
+      </c>
+      <c r="P66" s="3">
         <v>1100</v>
-      </c>
-      <c r="P66" s="3">
-        <v>2800</v>
       </c>
       <c r="Q66" s="3">
         <v>2800</v>
@@ -5746,28 +5904,28 @@
         <v>2800</v>
       </c>
       <c r="S66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="T66" s="3">
         <v>900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>700</v>
-      </c>
-      <c r="X66" s="3">
-        <v>400</v>
       </c>
       <c r="Y66" s="3">
         <v>400</v>
       </c>
       <c r="Z66" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AA66" s="3">
         <v>200</v>
@@ -5776,7 +5934,7 @@
         <v>200</v>
       </c>
       <c r="AC66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD66" s="3">
         <v>0</v>
@@ -5787,11 +5945,14 @@
       <c r="AF66" s="3">
         <v>0</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5825,8 +5986,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5920,8 +6082,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6015,8 +6180,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6110,8 +6278,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6205,103 +6376,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-31600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-29900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-26100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-24300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-23500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-22500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-20800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-19700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-18700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-18000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-9600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-8900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-200</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6395,8 +6572,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6490,8 +6670,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6585,103 +6768,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E76" s="3">
         <v>12500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2100</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>2400</v>
       </c>
       <c r="Z76" s="3">
         <v>2400</v>
       </c>
       <c r="AA76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB76" s="3">
         <v>2900</v>
       </c>
-      <c r="AB76" s="3">
-        <v>0</v>
-      </c>
       <c r="AC76" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE76" s="3">
         <v>2400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2500</v>
       </c>
-      <c r="AF76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6775,203 +6964,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-1900</v>
       </c>
       <c r="F81" s="3">
         <v>-1900</v>
       </c>
       <c r="G81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-300</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-500</v>
       </c>
       <c r="Z81" s="3">
         <v>-500</v>
       </c>
       <c r="AA81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-100</v>
       </c>
       <c r="AE81" s="3">
         <v>-100</v>
       </c>
       <c r="AF81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7005,25 +7203,26 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -7040,21 +7239,21 @@
       <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>100</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-100</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -7077,10 +7276,10 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>100</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
@@ -7088,11 +7287,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>100</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
@@ -7100,8 +7299,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7195,8 +7397,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7290,8 +7495,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7385,8 +7593,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7480,8 +7691,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7575,85 +7789,88 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S89" s="3">
+        <v>100</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-300</v>
       </c>
       <c r="Y89" s="3">
         <v>-300</v>
       </c>
       <c r="Z89" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AA89" s="3">
         <v>-400</v>
       </c>
       <c r="AB89" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
@@ -7667,11 +7884,14 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7705,8 +7925,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7749,8 +7970,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -7767,8 +7988,8 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -7800,8 +8021,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7895,8 +8119,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7990,8 +8217,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8025,29 +8255,29 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -8062,11 +8292,11 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-400</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
@@ -8082,11 +8312,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8120,31 +8353,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8215,8 +8449,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8310,8 +8547,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8405,8 +8645,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8500,8 +8743,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8509,20 +8755,20 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>8700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>2100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -8530,56 +8776,56 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>100</v>
+      </c>
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
-        <v>100</v>
-      </c>
       <c r="X100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>1500</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
@@ -8592,34 +8838,37 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8687,89 +8936,92 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-900</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>100</v>
-      </c>
       <c r="R102" s="3">
+        <v>100</v>
+      </c>
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
-        <v>100</v>
-      </c>
       <c r="W102" s="3">
+        <v>100</v>
+      </c>
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
         <v>0</v>
       </c>
@@ -8782,7 +9034,10 @@
       <c r="AF102" s="3">
         <v>0</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>NTRB</t>
   </si>
@@ -656,149 +656,153 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -806,31 +810,31 @@
         <v>600</v>
       </c>
       <c r="E8" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F8" s="3">
         <v>400</v>
       </c>
       <c r="G8" s="3">
+        <v>400</v>
+      </c>
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>700</v>
-      </c>
-      <c r="J8" s="3">
-        <v>500</v>
       </c>
       <c r="K8" s="3">
         <v>500</v>
       </c>
       <c r="L8" s="3">
+        <v>500</v>
+      </c>
+      <c r="M8" s="3">
         <v>600</v>
-      </c>
-      <c r="M8" s="3">
-        <v>500</v>
       </c>
       <c r="N8" s="3">
         <v>500</v>
@@ -839,44 +843,44 @@
         <v>500</v>
       </c>
       <c r="P8" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>400</v>
       </c>
       <c r="S8" s="3">
         <v>400</v>
       </c>
       <c r="T8" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="U8" s="3">
         <v>100</v>
       </c>
       <c r="V8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <v>100</v>
       </c>
       <c r="Y8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="3">
         <v>200</v>
       </c>
-      <c r="Z8" s="3">
-        <v>100</v>
-      </c>
       <c r="AA8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="3">
         <v>200</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
@@ -892,40 +896,43 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>300</v>
       </c>
       <c r="H9" s="3">
         <v>300</v>
       </c>
       <c r="I9" s="3">
+        <v>300</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>300</v>
       </c>
       <c r="M9" s="3">
         <v>300</v>
@@ -934,10 +941,10 @@
         <v>300</v>
       </c>
       <c r="O9" s="3">
+        <v>300</v>
+      </c>
+      <c r="P9" s="3">
         <v>400</v>
-      </c>
-      <c r="P9" s="3">
-        <v>200</v>
       </c>
       <c r="Q9" s="3">
         <v>200</v>
@@ -949,7 +956,7 @@
         <v>200</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U9" s="3">
         <v>100</v>
@@ -964,17 +971,17 @@
         <v>100</v>
       </c>
       <c r="Y9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z9" s="3">
         <v>200</v>
       </c>
-      <c r="Z9" s="3">
-        <v>100</v>
-      </c>
       <c r="AA9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB9" s="3">
         <v>200</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
@@ -993,19 +1000,22 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
-        <v>100</v>
-      </c>
       <c r="F10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>200</v>
@@ -1014,50 +1024,50 @@
         <v>200</v>
       </c>
       <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
-        <v>100</v>
-      </c>
       <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
         <v>300</v>
-      </c>
-      <c r="M10" s="3">
-        <v>200</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
       </c>
       <c r="O10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P10" s="3">
         <v>100</v>
       </c>
       <c r="Q10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3">
         <v>200</v>
       </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U10" s="3">
         <v>0</v>
       </c>
       <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
         <v>-100</v>
       </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
       <c r="X10" s="3">
         <v>0</v>
       </c>
@@ -1070,8 +1080,8 @@
       <c r="AA10" s="3">
         <v>0</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
+      <c r="AB10" s="3">
+        <v>0</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
@@ -1091,8 +1101,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1127,34 +1140,35 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>600</v>
       </c>
       <c r="H12" s="3">
         <v>600</v>
       </c>
       <c r="I12" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J12" s="3">
         <v>400</v>
       </c>
       <c r="K12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L12" s="3">
         <v>300</v>
@@ -1163,17 +1177,17 @@
         <v>300</v>
       </c>
       <c r="N12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,8 +1239,11 @@
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1323,38 +1340,41 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1362,11 +1382,11 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>2200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1380,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
-        <v>100</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>100</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1394,11 +1414,11 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
@@ -1406,12 +1426,12 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="3">
         <v>2500</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1421,8 +1441,11 @@
       <c r="AH14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1448,7 +1471,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1519,8 +1542,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1552,204 +1578,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1500</v>
       </c>
       <c r="J17" s="3">
         <v>1500</v>
       </c>
       <c r="K17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>700</v>
       </c>
       <c r="R17" s="3">
         <v>700</v>
       </c>
       <c r="S17" s="3">
+        <v>700</v>
+      </c>
+      <c r="T17" s="3">
         <v>400</v>
-      </c>
-      <c r="T17" s="3">
-        <v>300</v>
       </c>
       <c r="U17" s="3">
         <v>300</v>
       </c>
       <c r="V17" s="3">
+        <v>300</v>
+      </c>
+      <c r="W17" s="3">
         <v>600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2400</v>
       </c>
-      <c r="AE17" s="3">
-        <v>100</v>
-      </c>
       <c r="AF17" s="3">
         <v>100</v>
       </c>
       <c r="AG17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1400</v>
+        <v>-2000</v>
       </c>
       <c r="E18" s="3">
         <v>-1400</v>
       </c>
       <c r="F18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3">
         <v>-200</v>
       </c>
       <c r="V18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W18" s="3">
         <v>-600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-500</v>
       </c>
       <c r="AA18" s="3">
         <v>-500</v>
       </c>
       <c r="AB18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-100</v>
       </c>
       <c r="AF18" s="3">
         <v>-100</v>
       </c>
       <c r="AG18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1784,8 +1817,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1810,8 +1844,8 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1844,14 +1878,14 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1879,100 +1913,103 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-1000</v>
       </c>
       <c r="M21" s="3">
         <v>-1000</v>
       </c>
       <c r="N21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
       <c r="T21" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="U21" s="3">
         <v>-200</v>
       </c>
       <c r="V21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W21" s="3">
         <v>-900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-400</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>0</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
@@ -1980,8 +2017,11 @@
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2006,11 +2046,11 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2037,13 +2077,13 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
-        <v>100</v>
-      </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2051,8 +2091,8 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -2063,8 +2103,8 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2078,106 +2118,112 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-1900</v>
       </c>
       <c r="G23" s="3">
         <v>-1900</v>
       </c>
       <c r="H23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-500</v>
       </c>
       <c r="AA23" s="3">
         <v>-500</v>
       </c>
       <c r="AB23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-100</v>
       </c>
       <c r="AF23" s="3">
         <v>-100</v>
       </c>
       <c r="AG23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2202,8 +2248,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2274,8 +2320,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2372,204 +2421,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-1900</v>
       </c>
       <c r="G26" s="3">
         <v>-1900</v>
       </c>
       <c r="H26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-500</v>
       </c>
       <c r="AA26" s="3">
         <v>-500</v>
       </c>
       <c r="AB26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-100</v>
       </c>
       <c r="AF26" s="3">
         <v>-100</v>
       </c>
       <c r="AG26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-1900</v>
       </c>
       <c r="G27" s="3">
         <v>-1900</v>
       </c>
       <c r="H27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-500</v>
       </c>
       <c r="AA27" s="3">
         <v>-500</v>
       </c>
       <c r="AB27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-100</v>
       </c>
       <c r="AF27" s="3">
         <v>-100</v>
       </c>
       <c r="AG27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2666,8 +2724,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2764,8 +2825,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2862,8 +2926,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2960,8 +3027,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2986,8 +3056,8 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3020,14 +3090,14 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -3055,109 +3125,115 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-1900</v>
       </c>
       <c r="G33" s="3">
         <v>-1900</v>
       </c>
       <c r="H33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-500</v>
       </c>
       <c r="AA33" s="3">
         <v>-500</v>
       </c>
       <c r="AB33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-100</v>
       </c>
       <c r="AF33" s="3">
         <v>-100</v>
       </c>
       <c r="AG33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3254,209 +3330,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-1900</v>
       </c>
       <c r="G35" s="3">
         <v>-1900</v>
       </c>
       <c r="H35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-500</v>
       </c>
       <c r="AA35" s="3">
         <v>-500</v>
       </c>
       <c r="AB35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-100</v>
       </c>
       <c r="AF35" s="3">
         <v>-100</v>
       </c>
       <c r="AG35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3491,8 +3576,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3527,61 +3613,62 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
         <v>5700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
-      </c>
-      <c r="R41" s="3">
-        <v>200</v>
       </c>
       <c r="S41" s="3">
         <v>200</v>
       </c>
       <c r="T41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U41" s="3">
         <v>0</v>
@@ -3590,26 +3677,26 @@
         <v>0</v>
       </c>
       <c r="W41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1100</v>
       </c>
-      <c r="AC41" s="3">
-        <v>0</v>
-      </c>
       <c r="AD41" s="3">
         <v>0</v>
       </c>
@@ -3622,11 +3709,14 @@
       <c r="AG41" s="3">
         <v>0</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3723,8 +3813,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3741,7 +3834,7 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
@@ -3750,7 +3843,7 @@
         <v>200</v>
       </c>
       <c r="K43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
@@ -3768,16 +3861,16 @@
         <v>100</v>
       </c>
       <c r="Q43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3">
         <v>100</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3786,22 +3879,22 @@
         <v>0</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X43" s="3">
         <v>100</v>
       </c>
       <c r="Y43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
       <c r="AA43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3818,11 +3911,14 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3857,7 +3953,7 @@
         <v>200</v>
       </c>
       <c r="N44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O44" s="3">
         <v>100</v>
@@ -3872,10 +3968,10 @@
         <v>100</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
@@ -3892,17 +3988,17 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
       </c>
       <c r="AB44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
@@ -3916,11 +4012,14 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3945,32 +4044,32 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
-        <v>400</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
       </c>
       <c r="M45" s="3">
+        <v>400</v>
+      </c>
+      <c r="N45" s="3">
         <v>500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>400</v>
       </c>
       <c r="O45" s="3">
         <v>400</v>
       </c>
       <c r="P45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
+      <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3982,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>100</v>
@@ -4003,120 +4102,126 @@
         <v>100</v>
       </c>
       <c r="AD45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E46" s="3">
         <v>6200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>600</v>
-      </c>
-      <c r="R46" s="3">
-        <v>300</v>
       </c>
       <c r="S46" s="3">
         <v>300</v>
       </c>
       <c r="T46" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U46" s="3">
         <v>100</v>
       </c>
       <c r="V46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
         <v>300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1200</v>
       </c>
-      <c r="AC46" s="3">
-        <v>100</v>
-      </c>
       <c r="AD46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE46" s="3">
         <v>200</v>
       </c>
-      <c r="AE46" s="3">
-        <v>0</v>
-      </c>
       <c r="AF46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4141,8 +4246,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4213,8 +4318,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4222,7 +4330,7 @@
         <v>700</v>
       </c>
       <c r="E48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F48" s="3">
         <v>800</v>
@@ -4234,25 +4342,25 @@
         <v>800</v>
       </c>
       <c r="I48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J48" s="3">
         <v>900</v>
       </c>
       <c r="K48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L48" s="3">
         <v>1000</v>
       </c>
       <c r="M48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="N48" s="3">
         <v>1100</v>
       </c>
       <c r="O48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="P48" s="3">
         <v>1000</v>
@@ -4261,14 +4369,14 @@
         <v>1000</v>
       </c>
       <c r="R48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S48" s="3">
         <v>1100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
       </c>
-      <c r="T48" s="3">
-        <v>100</v>
-      </c>
       <c r="U48" s="3">
         <v>100</v>
       </c>
@@ -4291,10 +4399,10 @@
         <v>100</v>
       </c>
       <c r="AB48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>0</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
@@ -4311,19 +4419,22 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5600</v>
+        <v>2000</v>
       </c>
       <c r="E49" s="3">
         <v>5600</v>
       </c>
       <c r="F49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G49" s="3">
         <v>5700</v>
@@ -4335,13 +4446,13 @@
         <v>5700</v>
       </c>
       <c r="J49" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="K49" s="3">
         <v>5800</v>
       </c>
       <c r="L49" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="M49" s="3">
         <v>6200</v>
@@ -4350,10 +4461,10 @@
         <v>6200</v>
       </c>
       <c r="O49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="P49" s="3">
         <v>6300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>8500</v>
       </c>
       <c r="Q49" s="3">
         <v>8500</v>
@@ -4365,7 +4476,7 @@
         <v>8500</v>
       </c>
       <c r="T49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="U49" s="3">
         <v>2000</v>
@@ -4377,7 +4488,7 @@
         <v>2000</v>
       </c>
       <c r="X49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="Y49" s="3">
         <v>2100</v>
@@ -4388,8 +4499,8 @@
       <c r="AA49" s="3">
         <v>2100</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
+      <c r="AB49" s="3">
+        <v>2100</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
@@ -4397,20 +4508,23 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF49" s="3">
         <v>2400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2500</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4507,8 +4621,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4605,8 +4722,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4631,8 +4751,8 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4679,15 +4799,15 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1900</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,8 +4823,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4801,61 +4924,64 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E54" s="3">
         <v>12500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10100</v>
-      </c>
-      <c r="T54" s="3">
-        <v>2200</v>
       </c>
       <c r="U54" s="3">
         <v>2200</v>
@@ -4864,43 +4990,46 @@
         <v>2200</v>
       </c>
       <c r="W54" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="X54" s="3">
         <v>2400</v>
       </c>
       <c r="Y54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z54" s="3">
         <v>2500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3100</v>
       </c>
-      <c r="AC54" s="3">
-        <v>100</v>
-      </c>
       <c r="AD54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE54" s="3">
         <v>200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2500</v>
       </c>
-      <c r="AG54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,8 +5064,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4971,28 +5101,29 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>500</v>
       </c>
       <c r="J57" s="3">
         <v>500</v>
@@ -5004,58 +5135,58 @@
         <v>500</v>
       </c>
       <c r="M57" s="3">
+        <v>500</v>
+      </c>
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>600</v>
       </c>
       <c r="P57" s="3">
         <v>600</v>
       </c>
       <c r="Q57" s="3">
+        <v>600</v>
+      </c>
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
-      </c>
-      <c r="T57" s="3">
-        <v>700</v>
       </c>
       <c r="U57" s="3">
         <v>700</v>
       </c>
       <c r="V57" s="3">
+        <v>700</v>
+      </c>
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
-        <v>100</v>
-      </c>
       <c r="AC57" s="3">
         <v>100</v>
       </c>
       <c r="AD57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE57" s="3">
         <v>0</v>
@@ -5066,11 +5197,14 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5081,7 +5215,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
@@ -5093,10 +5227,10 @@
         <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5111,34 +5245,34 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>100</v>
+      </c>
+      <c r="R58" s="3">
         <v>1600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1600</v>
       </c>
-      <c r="T58" s="3">
-        <v>100</v>
-      </c>
       <c r="U58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3">
-        <v>100</v>
-      </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5152,23 +5286,26 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
+      <c r="AD58" s="3">
+        <v>0</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5179,10 +5316,10 @@
         <v>200</v>
       </c>
       <c r="F59" s="3">
+        <v>200</v>
+      </c>
+      <c r="G59" s="3">
         <v>300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>200</v>
       </c>
       <c r="H59" s="3">
         <v>200</v>
@@ -5206,14 +5343,14 @@
         <v>200</v>
       </c>
       <c r="O59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P59" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
-        <v>100</v>
-      </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
@@ -5221,28 +5358,28 @@
         <v>100</v>
       </c>
       <c r="T59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
       </c>
       <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
       <c r="Y59" s="3">
         <v>0</v>
       </c>
       <c r="Z59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -5262,85 +5399,88 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
-      </c>
-      <c r="L60" s="3">
-        <v>800</v>
       </c>
       <c r="M60" s="3">
         <v>800</v>
       </c>
       <c r="N60" s="3">
+        <v>800</v>
+      </c>
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2700</v>
-      </c>
-      <c r="R60" s="3">
-        <v>2600</v>
       </c>
       <c r="S60" s="3">
         <v>2600</v>
       </c>
       <c r="T60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="U60" s="3">
         <v>900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>700</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>400</v>
       </c>
       <c r="Z60" s="3">
         <v>400</v>
       </c>
       <c r="AA60" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AB60" s="3">
         <v>200</v>
@@ -5349,7 +5489,7 @@
         <v>200</v>
       </c>
       <c r="AD60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE60" s="3">
         <v>0</v>
@@ -5360,11 +5500,14 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5375,23 +5518,23 @@
         <v>100</v>
       </c>
       <c r="F61" s="3">
+        <v>100</v>
+      </c>
+      <c r="G61" s="3">
         <v>400</v>
       </c>
-      <c r="G61" s="3">
-        <v>100</v>
-      </c>
       <c r="H61" s="3">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>2100</v>
       </c>
       <c r="J61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
-        <v>100</v>
-      </c>
       <c r="L61" s="3">
         <v>100</v>
       </c>
@@ -5408,17 +5551,17 @@
         <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
         <v>200</v>
       </c>
       <c r="S61" s="3">
+        <v>200</v>
+      </c>
+      <c r="T61" s="3">
         <v>300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -5461,8 +5604,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5487,20 +5633,20 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+      <c r="O62" s="3">
+        <v>100</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -5517,8 +5663,8 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -5559,8 +5705,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5657,8 +5806,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5755,8 +5907,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5853,52 +6008,55 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>900</v>
       </c>
       <c r="L66" s="3">
         <v>900</v>
       </c>
       <c r="M66" s="3">
+        <v>900</v>
+      </c>
+      <c r="N66" s="3">
         <v>1000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>900</v>
       </c>
       <c r="O66" s="3">
         <v>900</v>
       </c>
       <c r="P66" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>2800</v>
       </c>
       <c r="R66" s="3">
         <v>2800</v>
@@ -5907,28 +6065,28 @@
         <v>2800</v>
       </c>
       <c r="T66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U66" s="3">
         <v>900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>700</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>400</v>
       </c>
       <c r="Z66" s="3">
         <v>400</v>
       </c>
       <c r="AA66" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AB66" s="3">
         <v>200</v>
@@ -5937,7 +6095,7 @@
         <v>200</v>
       </c>
       <c r="AD66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE66" s="3">
         <v>0</v>
@@ -5948,11 +6106,14 @@
       <c r="AG66" s="3">
         <v>0</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5987,8 +6148,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6085,8 +6247,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6183,8 +6348,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6281,8 +6449,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6379,106 +6550,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-32900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-31600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-29900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-26100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-24300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-23500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-22500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-20800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-19700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-18700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-12700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-200</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6575,8 +6752,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6673,8 +6853,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6771,106 +6954,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E76" s="3">
         <v>11200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2100</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>2400</v>
       </c>
       <c r="AA76" s="3">
         <v>2400</v>
       </c>
       <c r="AB76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC76" s="3">
         <v>2900</v>
       </c>
-      <c r="AC76" s="3">
-        <v>0</v>
-      </c>
       <c r="AD76" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF76" s="3">
         <v>2400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2500</v>
       </c>
-      <c r="AG76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6967,209 +7156,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-1900</v>
       </c>
       <c r="G81" s="3">
         <v>-1900</v>
       </c>
       <c r="H81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-500</v>
       </c>
       <c r="AA81" s="3">
         <v>-500</v>
       </c>
       <c r="AB81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-100</v>
       </c>
       <c r="AF81" s="3">
         <v>-100</v>
       </c>
       <c r="AG81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7204,8 +7402,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7225,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -7242,21 +7441,21 @@
       <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>100</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>-100</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -7279,10 +7478,10 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>100</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
@@ -7290,11 +7489,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>100</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
@@ -7302,8 +7501,11 @@
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7400,8 +7602,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7498,8 +7703,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7596,8 +7804,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7694,8 +7905,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7792,88 +8006,91 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T89" s="3">
+        <v>100</v>
+      </c>
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-300</v>
       </c>
       <c r="Z89" s="3">
         <v>-300</v>
       </c>
       <c r="AA89" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AB89" s="3">
         <v>-400</v>
       </c>
       <c r="AC89" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AD89" s="3">
         <v>0</v>
@@ -7887,11 +8104,14 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7926,8 +8146,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7973,8 +8194,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -7991,8 +8212,8 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -8024,8 +8245,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8122,8 +8346,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8220,8 +8447,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8258,29 +8488,29 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -8295,11 +8525,11 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-400</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
@@ -8315,11 +8545,14 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8354,8 +8587,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8380,8 +8614,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8452,8 +8686,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8550,8 +8787,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8648,8 +8888,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8746,32 +8989,35 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>8700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -8779,56 +9025,56 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>100</v>
+      </c>
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="X100" s="3">
-        <v>100</v>
-      </c>
       <c r="Y100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>1500</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
@@ -8841,11 +9087,14 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8870,8 +9119,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8939,92 +9188,95 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
-        <v>100</v>
-      </c>
       <c r="S102" s="3">
+        <v>100</v>
+      </c>
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
-        <v>100</v>
-      </c>
       <c r="X102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1100</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
         <v>0</v>
       </c>
@@ -9037,7 +9289,10 @@
       <c r="AG102" s="3">
         <v>0</v>
       </c>
-      <c r="AH102" s="3" t="s">
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
   <si>
     <t>NTRB</t>
   </si>
@@ -656,188 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E8" s="3">
         <v>600</v>
       </c>
       <c r="F8" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G8" s="3">
         <v>400</v>
       </c>
       <c r="H8" s="3">
+        <v>400</v>
+      </c>
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>700</v>
-      </c>
-      <c r="K8" s="3">
-        <v>500</v>
       </c>
       <c r="L8" s="3">
         <v>500</v>
       </c>
       <c r="M8" s="3">
+        <v>500</v>
+      </c>
+      <c r="N8" s="3">
         <v>600</v>
-      </c>
-      <c r="N8" s="3">
-        <v>500</v>
       </c>
       <c r="O8" s="3">
         <v>500</v>
@@ -846,44 +849,44 @@
         <v>500</v>
       </c>
       <c r="Q8" s="3">
+        <v>500</v>
+      </c>
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>400</v>
       </c>
       <c r="T8" s="3">
         <v>400</v>
       </c>
       <c r="U8" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
       </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <v>100</v>
       </c>
       <c r="Z8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
-        <v>100</v>
-      </c>
       <c r="AB8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC8" s="3">
         <v>200</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
@@ -899,11 +902,14 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -911,31 +917,31 @@
         <v>400</v>
       </c>
       <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>300</v>
       </c>
       <c r="I9" s="3">
         <v>300</v>
       </c>
       <c r="J9" s="3">
+        <v>300</v>
+      </c>
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
-      </c>
-      <c r="M9" s="3">
-        <v>300</v>
       </c>
       <c r="N9" s="3">
         <v>300</v>
@@ -944,10 +950,10 @@
         <v>300</v>
       </c>
       <c r="P9" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q9" s="3">
         <v>400</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>200</v>
       </c>
       <c r="R9" s="3">
         <v>200</v>
@@ -959,7 +965,7 @@
         <v>200</v>
       </c>
       <c r="U9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V9" s="3">
         <v>100</v>
@@ -974,17 +980,17 @@
         <v>100</v>
       </c>
       <c r="Z9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA9" s="3">
         <v>200</v>
       </c>
-      <c r="AA9" s="3">
-        <v>100</v>
-      </c>
       <c r="AB9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC9" s="3">
         <v>200</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,8 +1009,11 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1012,13 +1021,13 @@
         <v>300</v>
       </c>
       <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
       <c r="G10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>200</v>
@@ -1027,50 +1036,50 @@
         <v>200</v>
       </c>
       <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
       <c r="M10" s="3">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3">
         <v>300</v>
-      </c>
-      <c r="N10" s="3">
-        <v>200</v>
       </c>
       <c r="O10" s="3">
         <v>200</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q10" s="3">
         <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3">
         <v>200</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V10" s="3">
         <v>0</v>
       </c>
       <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
         <v>-100</v>
       </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
       <c r="Y10" s="3">
         <v>0</v>
       </c>
@@ -1083,8 +1092,8 @@
       <c r="AB10" s="3">
         <v>0</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
+      <c r="AC10" s="3">
+        <v>0</v>
       </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
@@ -1104,8 +1113,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1141,37 +1153,38 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>700</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>600</v>
       </c>
       <c r="I12" s="3">
         <v>600</v>
       </c>
       <c r="J12" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K12" s="3">
         <v>400</v>
       </c>
       <c r="L12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M12" s="3">
         <v>300</v>
@@ -1180,17 +1193,17 @@
         <v>300</v>
       </c>
       <c r="O12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1242,8 +1255,11 @@
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1343,41 +1359,44 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>3600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1385,11 +1404,11 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1403,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>100</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>100</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
@@ -1417,11 +1436,11 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
@@ -1429,12 +1448,12 @@
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF14" s="3">
         <v>2500</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1444,8 +1463,11 @@
       <c r="AI14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1474,7 +1496,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1545,8 +1567,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1579,210 +1604,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1500</v>
       </c>
       <c r="K17" s="3">
         <v>1500</v>
       </c>
       <c r="L17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
-      </c>
-      <c r="R17" s="3">
-        <v>700</v>
       </c>
       <c r="S17" s="3">
         <v>700</v>
       </c>
       <c r="T17" s="3">
+        <v>700</v>
+      </c>
+      <c r="U17" s="3">
         <v>400</v>
-      </c>
-      <c r="U17" s="3">
-        <v>300</v>
       </c>
       <c r="V17" s="3">
         <v>300</v>
       </c>
       <c r="W17" s="3">
+        <v>300</v>
+      </c>
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2400</v>
       </c>
-      <c r="AF17" s="3">
-        <v>100</v>
-      </c>
       <c r="AG17" s="3">
         <v>100</v>
       </c>
       <c r="AH17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2000</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-1400</v>
       </c>
       <c r="F18" s="3">
         <v>-1400</v>
       </c>
       <c r="G18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
         <v>-200</v>
       </c>
       <c r="W18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X18" s="3">
         <v>-600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-500</v>
       </c>
       <c r="AB18" s="3">
         <v>-500</v>
       </c>
       <c r="AC18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-100</v>
       </c>
       <c r="AG18" s="3">
         <v>-100</v>
       </c>
       <c r="AH18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1818,8 +1850,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1847,8 +1880,8 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1881,14 +1914,14 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1916,103 +1949,106 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-1000</v>
       </c>
       <c r="N21" s="3">
         <v>-1000</v>
       </c>
       <c r="O21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-400</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3">
         <v>-200</v>
       </c>
       <c r="W21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X21" s="3">
         <v>-900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-400</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>0</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
@@ -2020,8 +2056,11 @@
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2049,11 +2088,11 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2080,13 +2119,13 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
-        <v>100</v>
-      </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2094,8 +2133,8 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -2106,8 +2145,8 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2121,109 +2160,115 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1900</v>
       </c>
       <c r="H23" s="3">
         <v>-1900</v>
       </c>
       <c r="I23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-500</v>
       </c>
       <c r="AB23" s="3">
         <v>-500</v>
       </c>
       <c r="AC23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>-100</v>
       </c>
       <c r="AG23" s="3">
         <v>-100</v>
       </c>
       <c r="AH23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2251,8 +2296,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2323,8 +2368,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2424,210 +2472,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1900</v>
       </c>
       <c r="H26" s="3">
         <v>-1900</v>
       </c>
       <c r="I26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-500</v>
       </c>
       <c r="AB26" s="3">
         <v>-500</v>
       </c>
       <c r="AC26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>-100</v>
       </c>
       <c r="AG26" s="3">
         <v>-100</v>
       </c>
       <c r="AH26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1900</v>
       </c>
       <c r="H27" s="3">
         <v>-1900</v>
       </c>
       <c r="I27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-500</v>
       </c>
       <c r="AB27" s="3">
         <v>-500</v>
       </c>
       <c r="AC27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>-100</v>
       </c>
       <c r="AG27" s="3">
         <v>-100</v>
       </c>
       <c r="AH27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2727,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2828,8 +2888,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2929,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3030,8 +3096,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3059,8 +3128,8 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3093,14 +3162,14 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -3128,112 +3197,118 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1900</v>
       </c>
       <c r="H33" s="3">
         <v>-1900</v>
       </c>
       <c r="I33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-500</v>
       </c>
       <c r="AB33" s="3">
         <v>-500</v>
       </c>
       <c r="AC33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>-100</v>
       </c>
       <c r="AG33" s="3">
         <v>-100</v>
       </c>
       <c r="AH33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3333,215 +3408,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1900</v>
       </c>
       <c r="H35" s="3">
         <v>-1900</v>
       </c>
       <c r="I35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-500</v>
       </c>
       <c r="AB35" s="3">
         <v>-500</v>
       </c>
       <c r="AC35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>-100</v>
       </c>
       <c r="AG35" s="3">
         <v>-100</v>
       </c>
       <c r="AH35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3577,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3614,64 +3699,65 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
-      </c>
-      <c r="S41" s="3">
-        <v>200</v>
       </c>
       <c r="T41" s="3">
         <v>200</v>
       </c>
       <c r="U41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V41" s="3">
         <v>0</v>
@@ -3680,26 +3766,26 @@
         <v>0</v>
       </c>
       <c r="X41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1100</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
       <c r="AE41" s="3">
         <v>0</v>
       </c>
@@ -3712,11 +3798,14 @@
       <c r="AH41" s="3">
         <v>0</v>
       </c>
-      <c r="AI41" s="3" t="s">
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3816,8 +3905,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3837,7 +3929,7 @@
         <v>100</v>
       </c>
       <c r="I43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
@@ -3846,7 +3938,7 @@
         <v>200</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
@@ -3864,16 +3956,16 @@
         <v>100</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
         <v>100</v>
       </c>
       <c r="U43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3882,22 +3974,22 @@
         <v>0</v>
       </c>
       <c r="X43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="3">
         <v>100</v>
       </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
       <c r="AB43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3914,11 +4006,14 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-      <c r="AI43" s="3" t="s">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3956,7 +4051,7 @@
         <v>200</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
@@ -3971,10 +4066,10 @@
         <v>100</v>
       </c>
       <c r="T44" s="3">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
@@ -3991,17 +4086,17 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
       </c>
       <c r="AC44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE44" s="3">
         <v>0</v>
@@ -4015,11 +4110,14 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-      <c r="AI44" s="3" t="s">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4047,32 +4145,32 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
-        <v>400</v>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
       </c>
       <c r="N45" s="3">
+        <v>400</v>
+      </c>
+      <c r="O45" s="3">
         <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>400</v>
       </c>
       <c r="P45" s="3">
         <v>400</v>
       </c>
       <c r="Q45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3">
-        <v>0</v>
+      <c r="S45" s="3">
+        <v>200</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -4084,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
@@ -4105,123 +4203,129 @@
         <v>100</v>
       </c>
       <c r="AE45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF45" s="3">
         <v>200</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
-      </c>
       <c r="AG45" s="3">
         <v>0</v>
       </c>
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-      <c r="AI45" s="3" t="s">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>600</v>
-      </c>
-      <c r="S46" s="3">
-        <v>300</v>
       </c>
       <c r="T46" s="3">
         <v>300</v>
       </c>
       <c r="U46" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V46" s="3">
         <v>100</v>
       </c>
       <c r="W46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1200</v>
       </c>
-      <c r="AD46" s="3">
-        <v>100</v>
-      </c>
       <c r="AE46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF46" s="3">
         <v>200</v>
       </c>
-      <c r="AF46" s="3">
-        <v>0</v>
-      </c>
       <c r="AG46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI46" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4249,8 +4353,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4321,19 +4425,22 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E48" s="3">
         <v>700</v>
       </c>
       <c r="F48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="G48" s="3">
         <v>800</v>
@@ -4345,25 +4452,25 @@
         <v>800</v>
       </c>
       <c r="J48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K48" s="3">
         <v>900</v>
       </c>
       <c r="L48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="M48" s="3">
         <v>1000</v>
       </c>
       <c r="N48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="O48" s="3">
         <v>1100</v>
       </c>
       <c r="P48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="Q48" s="3">
         <v>1000</v>
@@ -4372,14 +4479,14 @@
         <v>1000</v>
       </c>
       <c r="S48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T48" s="3">
         <v>1100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1300</v>
       </c>
-      <c r="U48" s="3">
-        <v>100</v>
-      </c>
       <c r="V48" s="3">
         <v>100</v>
       </c>
@@ -4402,10 +4509,10 @@
         <v>100</v>
       </c>
       <c r="AC48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
@@ -4422,8 +4529,11 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4431,13 +4541,13 @@
         <v>2000</v>
       </c>
       <c r="E49" s="3">
-        <v>5600</v>
+        <v>2000</v>
       </c>
       <c r="F49" s="3">
         <v>5600</v>
       </c>
       <c r="G49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="H49" s="3">
         <v>5700</v>
@@ -4449,13 +4559,13 @@
         <v>5700</v>
       </c>
       <c r="K49" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="L49" s="3">
         <v>5800</v>
       </c>
       <c r="M49" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="N49" s="3">
         <v>6200</v>
@@ -4464,10 +4574,10 @@
         <v>6200</v>
       </c>
       <c r="P49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q49" s="3">
         <v>6300</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>8500</v>
       </c>
       <c r="R49" s="3">
         <v>8500</v>
@@ -4479,7 +4589,7 @@
         <v>8500</v>
       </c>
       <c r="U49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="V49" s="3">
         <v>2000</v>
@@ -4491,7 +4601,7 @@
         <v>2000</v>
       </c>
       <c r="Y49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="Z49" s="3">
         <v>2100</v>
@@ -4502,8 +4612,8 @@
       <c r="AB49" s="3">
         <v>2100</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
+      <c r="AC49" s="3">
+        <v>2100</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
@@ -4511,20 +4621,23 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG49" s="3">
         <v>2400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2500</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4624,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4725,8 +4841,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4754,8 +4873,8 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4802,15 +4921,15 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1900</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4826,8 +4945,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4927,64 +5049,67 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E54" s="3">
         <v>7500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10100</v>
-      </c>
-      <c r="U54" s="3">
-        <v>2200</v>
       </c>
       <c r="V54" s="3">
         <v>2200</v>
@@ -4993,43 +5118,46 @@
         <v>2200</v>
       </c>
       <c r="X54" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="Y54" s="3">
         <v>2400</v>
       </c>
       <c r="Z54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA54" s="3">
         <v>2500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3100</v>
       </c>
-      <c r="AD54" s="3">
-        <v>100</v>
-      </c>
       <c r="AE54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF54" s="3">
         <v>200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2500</v>
       </c>
-      <c r="AH54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="3" t="s">
+      <c r="AI54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5065,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5102,8 +5231,9 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5111,22 +5241,22 @@
         <v>700</v>
       </c>
       <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>500</v>
       </c>
       <c r="K57" s="3">
         <v>500</v>
@@ -5138,58 +5268,58 @@
         <v>500</v>
       </c>
       <c r="N57" s="3">
+        <v>500</v>
+      </c>
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>600</v>
       </c>
       <c r="Q57" s="3">
         <v>600</v>
       </c>
       <c r="R57" s="3">
+        <v>600</v>
+      </c>
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>800</v>
-      </c>
-      <c r="U57" s="3">
-        <v>700</v>
       </c>
       <c r="V57" s="3">
         <v>700</v>
       </c>
       <c r="W57" s="3">
+        <v>700</v>
+      </c>
+      <c r="X57" s="3">
         <v>800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>200</v>
       </c>
-      <c r="AC57" s="3">
-        <v>100</v>
-      </c>
       <c r="AD57" s="3">
         <v>100</v>
       </c>
       <c r="AE57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF57" s="3">
         <v>0</v>
@@ -5200,16 +5330,19 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-      <c r="AI57" s="3" t="s">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
@@ -5218,7 +5351,7 @@
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
@@ -5230,10 +5363,10 @@
         <v>200</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5248,34 +5381,34 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>100</v>
+      </c>
+      <c r="S58" s="3">
         <v>1600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3">
-        <v>100</v>
-      </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3">
-        <v>100</v>
-      </c>
       <c r="Z58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -5289,28 +5422,31 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>3</v>
+      <c r="AE58" s="3">
+        <v>0</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-      <c r="AI58" s="3" t="s">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
@@ -5319,10 +5455,10 @@
         <v>200</v>
       </c>
       <c r="G59" s="3">
+        <v>200</v>
+      </c>
+      <c r="H59" s="3">
         <v>300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>200</v>
@@ -5346,14 +5482,14 @@
         <v>200</v>
       </c>
       <c r="P59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="3">
+        <v>100</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
-        <v>100</v>
-      </c>
       <c r="S59" s="3">
         <v>100</v>
       </c>
@@ -5361,28 +5497,28 @@
         <v>100</v>
       </c>
       <c r="U59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
       </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>500</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
       <c r="Z59" s="3">
         <v>0</v>
       </c>
       <c r="AA59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -5402,88 +5538,91 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-      <c r="AI59" s="3" t="s">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
-      </c>
-      <c r="M60" s="3">
-        <v>800</v>
       </c>
       <c r="N60" s="3">
         <v>800</v>
       </c>
       <c r="O60" s="3">
+        <v>800</v>
+      </c>
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2700</v>
-      </c>
-      <c r="S60" s="3">
-        <v>2600</v>
       </c>
       <c r="T60" s="3">
         <v>2600</v>
       </c>
       <c r="U60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="V60" s="3">
         <v>900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>700</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>400</v>
       </c>
       <c r="AA60" s="3">
         <v>400</v>
       </c>
       <c r="AB60" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AC60" s="3">
         <v>200</v>
@@ -5492,7 +5631,7 @@
         <v>200</v>
       </c>
       <c r="AE60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF60" s="3">
         <v>0</v>
@@ -5503,11 +5642,14 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-      <c r="AI60" s="3" t="s">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5521,23 +5663,23 @@
         <v>100</v>
       </c>
       <c r="G61" s="3">
+        <v>100</v>
+      </c>
+      <c r="H61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
-        <v>100</v>
-      </c>
       <c r="I61" s="3">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>2100</v>
       </c>
       <c r="K61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
-        <v>100</v>
-      </c>
       <c r="M61" s="3">
         <v>100</v>
       </c>
@@ -5554,17 +5696,17 @@
         <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>200</v>
       </c>
       <c r="T61" s="3">
+        <v>200</v>
+      </c>
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5607,8 +5749,11 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5636,20 +5781,20 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>100</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -5666,8 +5811,8 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -5708,8 +5853,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5809,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5910,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6011,8 +6165,11 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6020,46 +6177,46 @@
         <v>1000</v>
       </c>
       <c r="E66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F66" s="3">
         <v>1300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>900</v>
       </c>
       <c r="M66" s="3">
         <v>900</v>
       </c>
       <c r="N66" s="3">
+        <v>900</v>
+      </c>
+      <c r="O66" s="3">
         <v>1000</v>
-      </c>
-      <c r="O66" s="3">
-        <v>900</v>
       </c>
       <c r="P66" s="3">
         <v>900</v>
       </c>
       <c r="Q66" s="3">
+        <v>900</v>
+      </c>
+      <c r="R66" s="3">
         <v>1100</v>
-      </c>
-      <c r="R66" s="3">
-        <v>2800</v>
       </c>
       <c r="S66" s="3">
         <v>2800</v>
@@ -6068,28 +6225,28 @@
         <v>2800</v>
       </c>
       <c r="U66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="V66" s="3">
         <v>900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>700</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>400</v>
       </c>
       <c r="AA66" s="3">
         <v>400</v>
       </c>
       <c r="AB66" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AC66" s="3">
         <v>200</v>
@@ -6098,7 +6255,7 @@
         <v>200</v>
       </c>
       <c r="AE66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF66" s="3">
         <v>0</v>
@@ -6109,11 +6266,14 @@
       <c r="AH66" s="3">
         <v>0</v>
       </c>
-      <c r="AI66" s="3" t="s">
+      <c r="AI66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6149,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6250,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6351,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6452,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6553,109 +6723,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-38500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-32900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-31600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-29900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-28000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-26100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-24300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-23500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-22500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-20800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-19700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-9300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-200</v>
       </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6755,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6856,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6957,109 +7139,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2100</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>2400</v>
       </c>
       <c r="AB76" s="3">
         <v>2400</v>
       </c>
       <c r="AC76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD76" s="3">
         <v>2900</v>
       </c>
-      <c r="AD76" s="3">
-        <v>0</v>
-      </c>
       <c r="AE76" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG76" s="3">
         <v>2400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2500</v>
       </c>
-      <c r="AH76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI76" s="3" t="s">
+      <c r="AI76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7159,215 +7347,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AI80" s="2" t="s">
+      <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1900</v>
       </c>
       <c r="H81" s="3">
         <v>-1900</v>
       </c>
       <c r="I81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-500</v>
       </c>
       <c r="AB81" s="3">
         <v>-500</v>
       </c>
       <c r="AC81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>-100</v>
       </c>
       <c r="AG81" s="3">
         <v>-100</v>
       </c>
       <c r="AH81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI81" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7403,8 +7600,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7427,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -7444,21 +7642,21 @@
       <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>100</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>-100</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
@@ -7481,10 +7679,10 @@
         <v>0</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>100</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
@@ -7492,11 +7690,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>100</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
@@ -7504,8 +7702,11 @@
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7605,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7706,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7807,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7908,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8009,91 +8222,94 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U89" s="3">
+        <v>100</v>
+      </c>
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-300</v>
       </c>
       <c r="AA89" s="3">
         <v>-300</v>
       </c>
       <c r="AB89" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AC89" s="3">
         <v>-400</v>
       </c>
       <c r="AD89" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AE89" s="3">
         <v>0</v>
@@ -8107,11 +8323,14 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8147,8 +8366,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8197,8 +8417,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -8215,8 +8435,8 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -8248,8 +8468,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8349,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8450,8 +8676,11 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8491,29 +8720,29 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8528,11 +8757,11 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
@@ -8548,11 +8777,14 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-      <c r="AI94" s="3" t="s">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8588,8 +8820,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8617,8 +8850,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8689,8 +8922,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8790,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8891,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8992,35 +9234,38 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>8700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>2100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -9028,56 +9273,56 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>100</v>
-      </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1500</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
@@ -9090,11 +9335,14 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9122,8 +9370,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9191,95 +9439,98 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
-        <v>100</v>
-      </c>
       <c r="T102" s="3">
+        <v>100</v>
+      </c>
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
-        <v>100</v>
-      </c>
       <c r="Y102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1100</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
         <v>0</v>
       </c>
@@ -9292,7 +9543,10 @@
       <c r="AH102" s="3">
         <v>0</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>NTRB</t>
   </si>
@@ -656,201 +656,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44135</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44043</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43951</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43861</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43769</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43677</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43585</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43496</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43404</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43312</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43220</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43131</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43039</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42947</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42855</v>
       </c>
-      <c r="AK7" s="2" t="s">
+      <c r="AL7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>700</v>
-      </c>
-      <c r="F8" s="3">
-        <v>600</v>
       </c>
       <c r="G8" s="3">
         <v>600</v>
       </c>
       <c r="H8" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I8" s="3">
         <v>400</v>
       </c>
       <c r="J8" s="3">
+        <v>400</v>
+      </c>
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>500</v>
       </c>
       <c r="N8" s="3">
         <v>500</v>
       </c>
       <c r="O8" s="3">
+        <v>500</v>
+      </c>
+      <c r="P8" s="3">
         <v>600</v>
-      </c>
-      <c r="P8" s="3">
-        <v>500</v>
       </c>
       <c r="Q8" s="3">
         <v>500</v>
@@ -859,44 +863,44 @@
         <v>500</v>
       </c>
       <c r="S8" s="3">
+        <v>500</v>
+      </c>
+      <c r="T8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>400</v>
       </c>
       <c r="V8" s="3">
         <v>400</v>
       </c>
       <c r="W8" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="X8" s="3">
         <v>100</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <v>100</v>
       </c>
       <c r="AB8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC8" s="3">
         <v>200</v>
       </c>
-      <c r="AC8" s="3">
-        <v>100</v>
-      </c>
       <c r="AD8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE8" s="3">
         <v>200</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
       <c r="AF8" s="3">
         <v>0</v>
       </c>
@@ -912,49 +916,52 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
-      <c r="AK8" s="3" t="s">
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>400</v>
       </c>
       <c r="F9" s="3">
         <v>400</v>
       </c>
       <c r="G9" s="3">
+        <v>400</v>
+      </c>
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>300</v>
       </c>
       <c r="K9" s="3">
         <v>300</v>
       </c>
       <c r="L9" s="3">
+        <v>300</v>
+      </c>
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
-      </c>
-      <c r="O9" s="3">
-        <v>300</v>
       </c>
       <c r="P9" s="3">
         <v>300</v>
@@ -963,10 +970,10 @@
         <v>300</v>
       </c>
       <c r="R9" s="3">
+        <v>300</v>
+      </c>
+      <c r="S9" s="3">
         <v>400</v>
-      </c>
-      <c r="S9" s="3">
-        <v>200</v>
       </c>
       <c r="T9" s="3">
         <v>200</v>
@@ -978,7 +985,7 @@
         <v>200</v>
       </c>
       <c r="W9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X9" s="3">
         <v>100</v>
@@ -993,17 +1000,17 @@
         <v>100</v>
       </c>
       <c r="AB9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC9" s="3">
         <v>200</v>
       </c>
-      <c r="AC9" s="3">
-        <v>100</v>
-      </c>
       <c r="AD9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE9" s="3">
         <v>200</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,28 +1029,31 @@
       <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>300</v>
       </c>
       <c r="F10" s="3">
         <v>300</v>
       </c>
       <c r="G10" s="3">
+        <v>300</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
-        <v>100</v>
-      </c>
       <c r="I10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
         <v>200</v>
@@ -1052,50 +1062,50 @@
         <v>200</v>
       </c>
       <c r="L10" s="3">
+        <v>200</v>
+      </c>
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
-        <v>100</v>
-      </c>
       <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
         <v>300</v>
-      </c>
-      <c r="P10" s="3">
-        <v>200</v>
       </c>
       <c r="Q10" s="3">
         <v>200</v>
       </c>
       <c r="R10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S10" s="3">
         <v>100</v>
       </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
         <v>200</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X10" s="3">
         <v>0</v>
       </c>
       <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
         <v>-100</v>
       </c>
-      <c r="Z10" s="3">
-        <v>0</v>
-      </c>
       <c r="AA10" s="3">
         <v>0</v>
       </c>
@@ -1108,8 +1118,8 @@
       <c r="AD10" s="3">
         <v>0</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
+      <c r="AE10" s="3">
+        <v>0</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
@@ -1129,8 +1139,11 @@
       <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1168,43 +1181,44 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>600</v>
       </c>
       <c r="K12" s="3">
         <v>600</v>
       </c>
       <c r="L12" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M12" s="3">
         <v>400</v>
       </c>
       <c r="N12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O12" s="3">
         <v>300</v>
@@ -1213,17 +1227,17 @@
         <v>300</v>
       </c>
       <c r="Q12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R12" s="3">
+        <v>100</v>
+      </c>
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1275,8 +1289,11 @@
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1382,8 +1399,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1393,36 +1413,36 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>3600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1430,11 +1450,11 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>2200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1448,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>100</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1462,11 +1482,11 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
@@ -1474,12 +1494,12 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH14" s="3">
         <v>2500</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1489,13 +1509,16 @@
       <c r="AK14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1525,7 +1548,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1596,8 +1619,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,222 +1658,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1500</v>
       </c>
       <c r="M17" s="3">
         <v>1500</v>
       </c>
       <c r="N17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
-      </c>
-      <c r="T17" s="3">
-        <v>700</v>
       </c>
       <c r="U17" s="3">
         <v>700</v>
       </c>
       <c r="V17" s="3">
+        <v>700</v>
+      </c>
+      <c r="W17" s="3">
         <v>400</v>
-      </c>
-      <c r="W17" s="3">
-        <v>300</v>
       </c>
       <c r="X17" s="3">
         <v>300</v>
       </c>
       <c r="Y17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2400</v>
       </c>
-      <c r="AH17" s="3">
-        <v>100</v>
-      </c>
       <c r="AI17" s="3">
         <v>100</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1400</v>
       </c>
       <c r="H18" s="3">
         <v>-1400</v>
       </c>
       <c r="I18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="X18" s="3">
         <v>-200</v>
       </c>
       <c r="Y18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-500</v>
       </c>
       <c r="AD18" s="3">
         <v>-500</v>
       </c>
       <c r="AE18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>-100</v>
       </c>
       <c r="AI18" s="3">
         <v>-100</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1885,8 +1918,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1920,8 +1954,8 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1954,14 +1988,14 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1989,109 +2023,112 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
-      <c r="AK20" s="3" t="s">
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1600</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-1000</v>
       </c>
       <c r="P21" s="3">
         <v>-1000</v>
       </c>
       <c r="Q21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R21" s="3">
         <v>-600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-400</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="X21" s="3">
         <v>-200</v>
       </c>
       <c r="Y21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-400</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="3" t="s">
-        <v>3</v>
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>0</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>3</v>
@@ -2099,8 +2136,11 @@
       <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2134,11 +2174,11 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2165,13 +2205,13 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
-        <v>100</v>
-      </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -2179,8 +2219,8 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
@@ -2191,8 +2231,8 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
@@ -2206,115 +2246,121 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1900</v>
       </c>
       <c r="J23" s="3">
         <v>-1900</v>
       </c>
       <c r="K23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-500</v>
       </c>
       <c r="AD23" s="3">
         <v>-500</v>
       </c>
       <c r="AE23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AH23" s="3">
-        <v>-100</v>
       </c>
       <c r="AI23" s="3">
         <v>-100</v>
       </c>
       <c r="AJ23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AK23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2348,8 +2394,8 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -2420,8 +2466,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2527,222 +2576,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-1900</v>
       </c>
       <c r="J26" s="3">
         <v>-1900</v>
       </c>
       <c r="K26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-500</v>
       </c>
       <c r="AD26" s="3">
         <v>-500</v>
       </c>
       <c r="AE26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>-100</v>
       </c>
       <c r="AI26" s="3">
         <v>-100</v>
       </c>
       <c r="AJ26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AK26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-1900</v>
       </c>
       <c r="J27" s="3">
         <v>-1900</v>
       </c>
       <c r="K27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-500</v>
       </c>
       <c r="AD27" s="3">
         <v>-500</v>
       </c>
       <c r="AE27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>-100</v>
       </c>
       <c r="AI27" s="3">
         <v>-100</v>
       </c>
       <c r="AJ27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AK27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2848,8 +2906,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2955,8 +3016,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3062,8 +3126,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3169,8 +3236,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3204,8 +3274,8 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -3238,14 +3308,14 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -3273,118 +3343,124 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
-      <c r="AK32" s="3" t="s">
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-1900</v>
       </c>
       <c r="J33" s="3">
         <v>-1900</v>
       </c>
       <c r="K33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-500</v>
       </c>
       <c r="AD33" s="3">
         <v>-500</v>
       </c>
       <c r="AE33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>-100</v>
       </c>
       <c r="AI33" s="3">
         <v>-100</v>
       </c>
       <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AK33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3490,227 +3566,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-1900</v>
       </c>
       <c r="J35" s="3">
         <v>-1900</v>
       </c>
       <c r="K35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-500</v>
       </c>
       <c r="AD35" s="3">
         <v>-500</v>
       </c>
       <c r="AE35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>-100</v>
       </c>
       <c r="AI35" s="3">
         <v>-100</v>
       </c>
       <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AK35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44135</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44043</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43951</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43861</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43769</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43677</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43585</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43496</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43404</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43312</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43220</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43131</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43039</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42947</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42855</v>
       </c>
-      <c r="AK38" s="2" t="s">
+      <c r="AL38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3748,8 +3833,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3787,70 +3873,71 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
         <v>7000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>300</v>
-      </c>
-      <c r="U41" s="3">
-        <v>200</v>
       </c>
       <c r="V41" s="3">
         <v>200</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X41" s="3">
         <v>0</v>
@@ -3859,26 +3946,26 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1100</v>
       </c>
-      <c r="AF41" s="3">
-        <v>0</v>
-      </c>
       <c r="AG41" s="3">
         <v>0</v>
       </c>
@@ -3891,11 +3978,14 @@
       <c r="AJ41" s="3">
         <v>0</v>
       </c>
-      <c r="AK41" s="3" t="s">
+      <c r="AK41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4001,17 +4091,20 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
-        <v>100</v>
-      </c>
       <c r="F43" s="3">
         <v>100</v>
       </c>
@@ -4028,7 +4121,7 @@
         <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
         <v>200</v>
@@ -4037,7 +4130,7 @@
         <v>200</v>
       </c>
       <c r="N43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O43" s="3">
         <v>100</v>
@@ -4055,16 +4148,16 @@
         <v>100</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
       </c>
       <c r="W43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -4073,22 +4166,22 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3">
         <v>100</v>
       </c>
       <c r="AB43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
       <c r="AD43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
@@ -4105,11 +4198,14 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
-      <c r="AK43" s="3" t="s">
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4117,7 +4213,7 @@
         <v>100</v>
       </c>
       <c r="E44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F44" s="3">
         <v>200</v>
@@ -4153,7 +4249,7 @@
         <v>200</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R44" s="3">
         <v>100</v>
@@ -4168,10 +4264,10 @@
         <v>100</v>
       </c>
       <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
@@ -4188,17 +4284,17 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
       </c>
       <c r="AE44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG44" s="3">
         <v>0</v>
@@ -4212,11 +4308,14 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
-      <c r="AK44" s="3" t="s">
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4250,32 +4349,32 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
-        <v>400</v>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O45" s="3">
         <v>400</v>
       </c>
       <c r="P45" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>400</v>
       </c>
       <c r="R45" s="3">
         <v>400</v>
       </c>
       <c r="S45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="U45" s="3">
+        <v>200</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -4287,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
@@ -4308,129 +4407,135 @@
         <v>100</v>
       </c>
       <c r="AG45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AH45" s="3">
-        <v>0</v>
-      </c>
       <c r="AI45" s="3">
         <v>0</v>
       </c>
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
-      <c r="AK45" s="3" t="s">
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>600</v>
-      </c>
-      <c r="U46" s="3">
-        <v>300</v>
       </c>
       <c r="V46" s="3">
         <v>300</v>
       </c>
       <c r="W46" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X46" s="3">
         <v>100</v>
       </c>
       <c r="Y46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3">
         <v>300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1200</v>
       </c>
-      <c r="AF46" s="3">
-        <v>100</v>
-      </c>
       <c r="AG46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH46" s="3">
         <v>200</v>
       </c>
-      <c r="AH46" s="3">
-        <v>0</v>
-      </c>
       <c r="AI46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4464,8 +4569,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4536,8 +4641,11 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4545,16 +4653,16 @@
         <v>700</v>
       </c>
       <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
         <v>800</v>
-      </c>
-      <c r="F48" s="3">
-        <v>700</v>
       </c>
       <c r="G48" s="3">
         <v>700</v>
       </c>
       <c r="H48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I48" s="3">
         <v>800</v>
@@ -4566,25 +4674,25 @@
         <v>800</v>
       </c>
       <c r="L48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="M48" s="3">
         <v>900</v>
       </c>
       <c r="N48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="O48" s="3">
         <v>1000</v>
       </c>
       <c r="P48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="Q48" s="3">
         <v>1100</v>
       </c>
       <c r="R48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="S48" s="3">
         <v>1000</v>
@@ -4593,14 +4701,14 @@
         <v>1000</v>
       </c>
       <c r="U48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V48" s="3">
         <v>1100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1300</v>
       </c>
-      <c r="W48" s="3">
-        <v>100</v>
-      </c>
       <c r="X48" s="3">
         <v>100</v>
       </c>
@@ -4623,10 +4731,10 @@
         <v>100</v>
       </c>
       <c r="AE48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>0</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>3</v>
@@ -4643,13 +4751,16 @@
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E49" s="3">
         <v>2000</v>
@@ -4658,13 +4769,13 @@
         <v>2000</v>
       </c>
       <c r="G49" s="3">
-        <v>5600</v>
+        <v>2000</v>
       </c>
       <c r="H49" s="3">
         <v>5600</v>
       </c>
       <c r="I49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="J49" s="3">
         <v>5700</v>
@@ -4676,13 +4787,13 @@
         <v>5700</v>
       </c>
       <c r="M49" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="N49" s="3">
         <v>5800</v>
       </c>
       <c r="O49" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="P49" s="3">
         <v>6200</v>
@@ -4691,10 +4802,10 @@
         <v>6200</v>
       </c>
       <c r="R49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="S49" s="3">
         <v>6300</v>
-      </c>
-      <c r="S49" s="3">
-        <v>8500</v>
       </c>
       <c r="T49" s="3">
         <v>8500</v>
@@ -4706,7 +4817,7 @@
         <v>8500</v>
       </c>
       <c r="W49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="X49" s="3">
         <v>2000</v>
@@ -4718,7 +4829,7 @@
         <v>2000</v>
       </c>
       <c r="AA49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AB49" s="3">
         <v>2100</v>
@@ -4729,8 +4840,8 @@
       <c r="AD49" s="3">
         <v>2100</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
+      <c r="AE49" s="3">
+        <v>2100</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>3</v>
@@ -4738,20 +4849,23 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI49" s="3">
         <v>2400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4857,8 +4971,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4964,8 +5081,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4999,8 +5119,8 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -5047,15 +5167,15 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1900</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5071,8 +5191,11 @@
       <c r="AK52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5178,70 +5301,73 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E54" s="3">
         <v>10200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10100</v>
-      </c>
-      <c r="W54" s="3">
-        <v>2200</v>
       </c>
       <c r="X54" s="3">
         <v>2200</v>
@@ -5250,43 +5376,46 @@
         <v>2200</v>
       </c>
       <c r="Z54" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="AA54" s="3">
         <v>2400</v>
       </c>
       <c r="AB54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC54" s="3">
         <v>2500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3100</v>
       </c>
-      <c r="AF54" s="3">
-        <v>100</v>
-      </c>
       <c r="AG54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH54" s="3">
         <v>200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="3" t="s">
+      <c r="AK54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5324,8 +5453,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5363,37 +5493,38 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
-      </c>
-      <c r="E57" s="3">
-        <v>700</v>
       </c>
       <c r="F57" s="3">
         <v>700</v>
       </c>
       <c r="G57" s="3">
+        <v>700</v>
+      </c>
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>500</v>
       </c>
       <c r="M57" s="3">
         <v>500</v>
@@ -5405,58 +5536,58 @@
         <v>500</v>
       </c>
       <c r="P57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
-      </c>
-      <c r="R57" s="3">
-        <v>600</v>
       </c>
       <c r="S57" s="3">
         <v>600</v>
       </c>
       <c r="T57" s="3">
+        <v>600</v>
+      </c>
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
-      </c>
-      <c r="W57" s="3">
-        <v>700</v>
       </c>
       <c r="X57" s="3">
         <v>700</v>
       </c>
       <c r="Y57" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3">
-        <v>100</v>
-      </c>
       <c r="AF57" s="3">
         <v>100</v>
       </c>
       <c r="AG57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH57" s="3">
         <v>0</v>
@@ -5467,11 +5598,14 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
-      <c r="AK57" s="3" t="s">
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5482,7 +5616,7 @@
         <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>100</v>
@@ -5491,7 +5625,7 @@
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
@@ -5503,10 +5637,10 @@
         <v>200</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -5521,34 +5655,34 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>100</v>
+      </c>
+      <c r="U58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1600</v>
       </c>
-      <c r="W58" s="3">
-        <v>100</v>
-      </c>
       <c r="X58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3">
-        <v>100</v>
-      </c>
       <c r="AB58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5562,23 +5696,26 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>3</v>
+      <c r="AG58" s="3">
+        <v>0</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
-      <c r="AK58" s="3" t="s">
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5589,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
         <v>200</v>
@@ -5598,10 +5735,10 @@
         <v>200</v>
       </c>
       <c r="I59" s="3">
+        <v>200</v>
+      </c>
+      <c r="J59" s="3">
         <v>300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>200</v>
@@ -5625,14 +5762,14 @@
         <v>200</v>
       </c>
       <c r="R59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S59" s="3">
+        <v>100</v>
+      </c>
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
-        <v>100</v>
-      </c>
       <c r="U59" s="3">
         <v>100</v>
       </c>
@@ -5640,28 +5777,28 @@
         <v>100</v>
       </c>
       <c r="W59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
       <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
         <v>900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>500</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
       <c r="AB59" s="3">
         <v>0</v>
       </c>
       <c r="AC59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5681,94 +5818,97 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
-      <c r="AK59" s="3" t="s">
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
-      </c>
-      <c r="O60" s="3">
-        <v>800</v>
       </c>
       <c r="P60" s="3">
         <v>800</v>
       </c>
       <c r="Q60" s="3">
+        <v>800</v>
+      </c>
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2700</v>
-      </c>
-      <c r="U60" s="3">
-        <v>2600</v>
       </c>
       <c r="V60" s="3">
         <v>2600</v>
       </c>
       <c r="W60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X60" s="3">
         <v>900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>700</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>400</v>
       </c>
       <c r="AC60" s="3">
         <v>400</v>
       </c>
       <c r="AD60" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AE60" s="3">
         <v>200</v>
@@ -5777,7 +5917,7 @@
         <v>200</v>
       </c>
       <c r="AG60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AH60" s="3">
         <v>0</v>
@@ -5788,11 +5928,14 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
-      <c r="AK60" s="3" t="s">
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5812,23 +5955,23 @@
         <v>100</v>
       </c>
       <c r="I61" s="3">
+        <v>100</v>
+      </c>
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="J61" s="3">
-        <v>100</v>
-      </c>
       <c r="K61" s="3">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>2100</v>
       </c>
       <c r="M61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
-        <v>100</v>
-      </c>
       <c r="O61" s="3">
         <v>100</v>
       </c>
@@ -5845,17 +5988,17 @@
         <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>200</v>
       </c>
       <c r="V61" s="3">
+        <v>200</v>
+      </c>
+      <c r="W61" s="3">
         <v>300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -5898,8 +6041,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5933,20 +6079,20 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>100</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -5963,8 +6109,8 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -6005,8 +6151,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6112,8 +6261,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6219,8 +6371,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6326,61 +6481,64 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1700</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1000</v>
       </c>
       <c r="F66" s="3">
         <v>1000</v>
       </c>
       <c r="G66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H66" s="3">
         <v>1300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>900</v>
       </c>
       <c r="O66" s="3">
         <v>900</v>
       </c>
       <c r="P66" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>900</v>
       </c>
       <c r="R66" s="3">
         <v>900</v>
       </c>
       <c r="S66" s="3">
+        <v>900</v>
+      </c>
+      <c r="T66" s="3">
         <v>1100</v>
-      </c>
-      <c r="T66" s="3">
-        <v>2800</v>
       </c>
       <c r="U66" s="3">
         <v>2800</v>
@@ -6389,28 +6547,28 @@
         <v>2800</v>
       </c>
       <c r="W66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X66" s="3">
         <v>900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>700</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>400</v>
       </c>
       <c r="AC66" s="3">
         <v>400</v>
       </c>
       <c r="AD66" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AE66" s="3">
         <v>200</v>
@@ -6419,7 +6577,7 @@
         <v>200</v>
       </c>
       <c r="AG66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AH66" s="3">
         <v>0</v>
@@ -6430,11 +6588,14 @@
       <c r="AJ66" s="3">
         <v>0</v>
       </c>
-      <c r="AK66" s="3" t="s">
+      <c r="AK66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL66" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6472,8 +6633,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6579,8 +6741,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6686,8 +6851,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6793,8 +6961,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6900,115 +7071,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-41900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-39900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-38500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-32900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-31600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-29900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-28000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-26100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-22500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-20800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-18700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-14200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-12700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-11800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-9600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-9500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-200</v>
       </c>
-      <c r="AK72" s="3" t="s">
+      <c r="AL72" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7114,8 +7291,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7221,8 +7401,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7328,115 +7511,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E76" s="3">
         <v>8500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>2400</v>
       </c>
       <c r="AD76" s="3">
         <v>2400</v>
       </c>
       <c r="AE76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF76" s="3">
         <v>2900</v>
       </c>
-      <c r="AF76" s="3">
-        <v>0</v>
-      </c>
       <c r="AG76" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI76" s="3">
         <v>2400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK76" s="3" t="s">
+      <c r="AK76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7542,227 +7731,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44135</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44043</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43951</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43861</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43769</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43677</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43585</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43496</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43404</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43312</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43220</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43131</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43039</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42947</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42855</v>
       </c>
-      <c r="AK80" s="2" t="s">
+      <c r="AL80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-1900</v>
       </c>
       <c r="J81" s="3">
         <v>-1900</v>
       </c>
       <c r="K81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-500</v>
       </c>
       <c r="AD81" s="3">
         <v>-500</v>
       </c>
       <c r="AE81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>-100</v>
       </c>
       <c r="AI81" s="3">
         <v>-100</v>
       </c>
       <c r="AJ81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK81" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AK81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7800,8 +7998,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7830,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -7847,21 +8046,21 @@
       <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>100</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>-100</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
@@ -7884,10 +8083,10 @@
         <v>0</v>
       </c>
       <c r="AD83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>100</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
@@ -7895,11 +8094,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>100</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
@@ -7907,8 +8106,11 @@
       <c r="AK83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8014,8 +8216,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8121,8 +8326,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8228,8 +8436,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8335,8 +8546,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8442,97 +8656,100 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1300</v>
+        <v>-1800</v>
       </c>
       <c r="E89" s="3">
         <v>-1300</v>
       </c>
       <c r="F89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W89" s="3">
+        <v>100</v>
+      </c>
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-300</v>
       </c>
       <c r="AC89" s="3">
         <v>-300</v>
       </c>
       <c r="AD89" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AE89" s="3">
         <v>-400</v>
       </c>
       <c r="AF89" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AG89" s="3">
         <v>0</v>
@@ -8546,11 +8763,14 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
-      <c r="AK89" s="3" t="s">
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8588,8 +8808,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8644,8 +8865,8 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -8662,8 +8883,8 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8695,8 +8916,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8802,8 +9026,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8909,8 +9136,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8956,29 +9186,29 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -8993,11 +9223,11 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-400</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
@@ -9013,11 +9243,14 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
-      <c r="AK94" s="3" t="s">
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9055,8 +9288,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9090,8 +9324,8 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -9162,8 +9396,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9269,8 +9506,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9376,8 +9616,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9483,41 +9726,44 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>5300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>8700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>2100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -9525,56 +9771,56 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>400</v>
       </c>
-      <c r="AA100" s="3">
-        <v>100</v>
-      </c>
       <c r="AB100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>1500</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
@@ -9587,11 +9833,14 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
-      <c r="AK100" s="3" t="s">
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9625,8 +9874,8 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -9694,101 +9943,104 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
-      <c r="AK101" s="3" t="s">
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>4000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-900</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
-        <v>100</v>
-      </c>
       <c r="V102" s="3">
+        <v>100</v>
+      </c>
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>100</v>
-      </c>
       <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1100</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
         <v>0</v>
       </c>
@@ -9801,7 +10053,10 @@
       <c r="AJ102" s="3">
         <v>0</v>
       </c>
-      <c r="AK102" s="3" t="s">
+      <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTRB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>NTRB</t>
   </si>
@@ -656,208 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45961</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43951</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43677</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43585</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43496</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43312</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43220</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43131</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42947</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AM7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>700</v>
-      </c>
-      <c r="G8" s="3">
-        <v>600</v>
       </c>
       <c r="H8" s="3">
         <v>600</v>
       </c>
       <c r="I8" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="J8" s="3">
         <v>400</v>
       </c>
       <c r="K8" s="3">
+        <v>400</v>
+      </c>
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>500</v>
       </c>
       <c r="O8" s="3">
         <v>500</v>
       </c>
       <c r="P8" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q8" s="3">
         <v>600</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>500</v>
       </c>
       <c r="R8" s="3">
         <v>500</v>
@@ -866,44 +870,44 @@
         <v>500</v>
       </c>
       <c r="T8" s="3">
+        <v>500</v>
+      </c>
+      <c r="U8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>200</v>
-      </c>
-      <c r="V8" s="3">
-        <v>400</v>
       </c>
       <c r="W8" s="3">
         <v>400</v>
       </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Y8" s="3">
         <v>100</v>
       </c>
       <c r="Z8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <v>100</v>
       </c>
       <c r="AC8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD8" s="3">
         <v>200</v>
       </c>
-      <c r="AD8" s="3">
-        <v>100</v>
-      </c>
       <c r="AE8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF8" s="3">
         <v>200</v>
       </c>
-      <c r="AF8" s="3">
-        <v>0</v>
-      </c>
       <c r="AG8" s="3">
         <v>0</v>
       </c>
@@ -919,11 +923,14 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
-      <c r="AL8" s="3" t="s">
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -931,40 +938,40 @@
         <v>300</v>
       </c>
       <c r="E9" s="3">
+        <v>300</v>
+      </c>
+      <c r="F9" s="3">
         <v>500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>400</v>
       </c>
       <c r="G9" s="3">
         <v>400</v>
       </c>
       <c r="H9" s="3">
+        <v>400</v>
+      </c>
+      <c r="I9" s="3">
         <v>500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>300</v>
       </c>
       <c r="M9" s="3">
+        <v>300</v>
+      </c>
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
-      </c>
-      <c r="P9" s="3">
-        <v>300</v>
       </c>
       <c r="Q9" s="3">
         <v>300</v>
@@ -973,10 +980,10 @@
         <v>300</v>
       </c>
       <c r="S9" s="3">
+        <v>300</v>
+      </c>
+      <c r="T9" s="3">
         <v>400</v>
-      </c>
-      <c r="T9" s="3">
-        <v>200</v>
       </c>
       <c r="U9" s="3">
         <v>200</v>
@@ -988,7 +995,7 @@
         <v>200</v>
       </c>
       <c r="X9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y9" s="3">
         <v>100</v>
@@ -1003,17 +1010,17 @@
         <v>100</v>
       </c>
       <c r="AC9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD9" s="3">
         <v>200</v>
       </c>
-      <c r="AD9" s="3">
-        <v>100</v>
-      </c>
       <c r="AE9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF9" s="3">
         <v>200</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1032,8 +1039,11 @@
       <c r="AL9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1041,22 +1051,22 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>300</v>
       </c>
       <c r="G10" s="3">
         <v>300</v>
       </c>
       <c r="H10" s="3">
+        <v>300</v>
+      </c>
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
-        <v>100</v>
-      </c>
       <c r="J10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>200</v>
@@ -1065,50 +1075,50 @@
         <v>200</v>
       </c>
       <c r="M10" s="3">
+        <v>200</v>
+      </c>
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
-        <v>100</v>
-      </c>
       <c r="P10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3">
         <v>300</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>200</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
       </c>
       <c r="S10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T10" s="3">
         <v>100</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>200</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y10" s="3">
         <v>0</v>
       </c>
       <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="3">
         <v>-100</v>
       </c>
-      <c r="AA10" s="3">
-        <v>0</v>
-      </c>
       <c r="AB10" s="3">
         <v>0</v>
       </c>
@@ -1121,8 +1131,8 @@
       <c r="AE10" s="3">
         <v>0</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
+      <c r="AF10" s="3">
+        <v>0</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
@@ -1142,8 +1152,11 @@
       <c r="AL10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1182,46 +1195,47 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>600</v>
       </c>
       <c r="L12" s="3">
         <v>600</v>
       </c>
       <c r="M12" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N12" s="3">
         <v>400</v>
       </c>
       <c r="O12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P12" s="3">
         <v>300</v>
@@ -1230,17 +1244,17 @@
         <v>300</v>
       </c>
       <c r="R12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S12" s="3">
+        <v>100</v>
+      </c>
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1292,8 +1306,11 @@
       <c r="AL12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1402,8 +1419,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1416,36 +1436,36 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>3600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1453,11 +1473,11 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>2200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1471,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>100</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
@@ -1485,11 +1505,11 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
@@ -1497,12 +1517,12 @@
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI14" s="3">
         <v>2500</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1512,8 +1532,11 @@
       <c r="AL14" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1521,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1551,7 +1574,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1622,8 +1645,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1659,228 +1685,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E17" s="3">
         <v>4200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1500</v>
       </c>
       <c r="N17" s="3">
         <v>1500</v>
       </c>
       <c r="O17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
-      </c>
-      <c r="U17" s="3">
-        <v>700</v>
       </c>
       <c r="V17" s="3">
         <v>700</v>
       </c>
       <c r="W17" s="3">
+        <v>700</v>
+      </c>
+      <c r="X17" s="3">
         <v>400</v>
-      </c>
-      <c r="X17" s="3">
-        <v>300</v>
       </c>
       <c r="Y17" s="3">
         <v>300</v>
       </c>
       <c r="Z17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2400</v>
       </c>
-      <c r="AI17" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ17" s="3">
         <v>100</v>
       </c>
       <c r="AK17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AL17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1400</v>
       </c>
       <c r="I18" s="3">
         <v>-1400</v>
       </c>
       <c r="J18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3">
         <v>-200</v>
       </c>
       <c r="Z18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-500</v>
       </c>
       <c r="AE18" s="3">
         <v>-500</v>
       </c>
       <c r="AF18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ18" s="3">
         <v>-100</v>
       </c>
       <c r="AK18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1919,13 +1952,14 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-100</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1936,8 +1970,8 @@
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>-200</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1957,8 +1991,8 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1991,14 +2025,14 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-400</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -2026,112 +2060,115 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
-      <c r="AL20" s="3" t="s">
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1600</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q21" s="3">
         <v>-1000</v>
       </c>
       <c r="R21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S21" s="3">
         <v>-600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-400</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
       <c r="X21" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
         <v>-200</v>
       </c>
       <c r="Z21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-400</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="3" t="s">
-        <v>3</v>
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ21" s="3">
+        <v>0</v>
       </c>
       <c r="AK21" s="3" t="s">
         <v>3</v>
@@ -2139,8 +2176,11 @@
       <c r="AL21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2177,11 +2217,11 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2208,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
-        <v>100</v>
-      </c>
       <c r="AA22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2222,8 +2262,8 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
@@ -2234,8 +2274,8 @@
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
@@ -2249,118 +2289,124 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1900</v>
       </c>
       <c r="K23" s="3">
         <v>-1900</v>
       </c>
       <c r="L23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-500</v>
       </c>
       <c r="AE23" s="3">
         <v>-500</v>
       </c>
       <c r="AF23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AI23" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ23" s="3">
         <v>-100</v>
       </c>
       <c r="AK23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2397,8 +2443,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2469,8 +2515,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2579,228 +2628,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-1900</v>
       </c>
       <c r="K26" s="3">
         <v>-1900</v>
       </c>
       <c r="L26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M26" s="3">
         <v>-1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-500</v>
       </c>
       <c r="AE26" s="3">
         <v>-500</v>
       </c>
       <c r="AF26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AI26" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ26" s="3">
         <v>-100</v>
       </c>
       <c r="AK26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-1900</v>
       </c>
       <c r="K27" s="3">
         <v>-1900</v>
       </c>
       <c r="L27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-500</v>
       </c>
       <c r="AE27" s="3">
         <v>-500</v>
       </c>
       <c r="AF27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AI27" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ27" s="3">
         <v>-100</v>
       </c>
       <c r="AK27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2909,8 +2967,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3019,8 +3080,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3129,8 +3193,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3239,13 +3306,16 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>100</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -3256,8 +3326,8 @@
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>200</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -3277,8 +3347,8 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3311,14 +3381,14 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>400</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3346,121 +3416,127 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
-      <c r="AL32" s="3" t="s">
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-1900</v>
       </c>
       <c r="K33" s="3">
         <v>-1900</v>
       </c>
       <c r="L33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M33" s="3">
         <v>-1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-500</v>
       </c>
       <c r="AE33" s="3">
         <v>-500</v>
       </c>
       <c r="AF33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AI33" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ33" s="3">
         <v>-100</v>
       </c>
       <c r="AK33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL33" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3569,233 +3645,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-1900</v>
       </c>
       <c r="K35" s="3">
         <v>-1900</v>
       </c>
       <c r="L35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M35" s="3">
         <v>-1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-500</v>
       </c>
       <c r="AE35" s="3">
         <v>-500</v>
       </c>
       <c r="AF35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AI35" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ35" s="3">
         <v>-100</v>
       </c>
       <c r="AK35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45961</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43951</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43677</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43585</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43496</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43312</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43220</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43131</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42947</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2" t="s">
+      <c r="AM38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3834,8 +3919,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3874,73 +3960,74 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E41" s="3">
         <v>5300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>300</v>
-      </c>
-      <c r="V41" s="3">
-        <v>200</v>
       </c>
       <c r="W41" s="3">
         <v>200</v>
       </c>
       <c r="X41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y41" s="3">
         <v>0</v>
@@ -3949,26 +4036,26 @@
         <v>0</v>
       </c>
       <c r="AA41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1100</v>
       </c>
-      <c r="AG41" s="3">
-        <v>0</v>
-      </c>
       <c r="AH41" s="3">
         <v>0</v>
       </c>
@@ -3981,11 +4068,14 @@
       <c r="AK41" s="3">
         <v>0</v>
       </c>
-      <c r="AL41" s="3" t="s">
+      <c r="AL41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4094,8 +4184,11 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4103,11 +4196,11 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
-        <v>100</v>
-      </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
@@ -4124,7 +4217,7 @@
         <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
@@ -4133,7 +4226,7 @@
         <v>200</v>
       </c>
       <c r="O43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P43" s="3">
         <v>100</v>
@@ -4151,16 +4244,16 @@
         <v>100</v>
       </c>
       <c r="U43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W43" s="3">
         <v>100</v>
       </c>
       <c r="X43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -4169,22 +4262,22 @@
         <v>0</v>
       </c>
       <c r="AA43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="3">
         <v>100</v>
       </c>
       <c r="AC43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
       <c r="AE43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
@@ -4201,11 +4294,14 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
-      <c r="AL43" s="3" t="s">
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4216,7 +4312,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G44" s="3">
         <v>200</v>
@@ -4252,7 +4348,7 @@
         <v>200</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S44" s="3">
         <v>100</v>
@@ -4267,10 +4363,10 @@
         <v>100</v>
       </c>
       <c r="W44" s="3">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
@@ -4287,17 +4383,17 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE44" s="3">
         <v>0</v>
       </c>
       <c r="AF44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH44" s="3">
         <v>0</v>
@@ -4311,11 +4407,14 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
-      <c r="AL44" s="3" t="s">
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4352,32 +4451,32 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
-        <v>400</v>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P45" s="3">
         <v>400</v>
       </c>
       <c r="Q45" s="3">
+        <v>400</v>
+      </c>
+      <c r="R45" s="3">
         <v>500</v>
-      </c>
-      <c r="R45" s="3">
-        <v>400</v>
       </c>
       <c r="S45" s="3">
         <v>400</v>
       </c>
       <c r="T45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W45" s="3">
-        <v>0</v>
+      <c r="V45" s="3">
+        <v>200</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
@@ -4389,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="AA45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
         <v>100</v>
@@ -4410,132 +4509,138 @@
         <v>100</v>
       </c>
       <c r="AH45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI45" s="3">
         <v>200</v>
       </c>
-      <c r="AI45" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
       <c r="AK45" s="3">
         <v>0</v>
       </c>
-      <c r="AL45" s="3" t="s">
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>600</v>
-      </c>
-      <c r="V46" s="3">
-        <v>300</v>
       </c>
       <c r="W46" s="3">
         <v>300</v>
       </c>
       <c r="X46" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Y46" s="3">
         <v>100</v>
       </c>
       <c r="Z46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="3">
         <v>300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1200</v>
       </c>
-      <c r="AG46" s="3">
-        <v>100</v>
-      </c>
       <c r="AH46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI46" s="3">
         <v>200</v>
       </c>
-      <c r="AI46" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL46" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4572,8 +4677,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4644,28 +4749,31 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E48" s="3">
         <v>700</v>
       </c>
       <c r="F48" s="3">
+        <v>700</v>
+      </c>
+      <c r="G48" s="3">
         <v>800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>700</v>
       </c>
       <c r="H48" s="3">
         <v>700</v>
       </c>
       <c r="I48" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J48" s="3">
         <v>800</v>
@@ -4677,25 +4785,25 @@
         <v>800</v>
       </c>
       <c r="M48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="N48" s="3">
         <v>900</v>
       </c>
       <c r="O48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="P48" s="3">
         <v>1000</v>
       </c>
       <c r="Q48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="R48" s="3">
         <v>1100</v>
       </c>
       <c r="S48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="T48" s="3">
         <v>1000</v>
@@ -4704,14 +4812,14 @@
         <v>1000</v>
       </c>
       <c r="V48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W48" s="3">
         <v>1100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1300</v>
       </c>
-      <c r="X48" s="3">
-        <v>100</v>
-      </c>
       <c r="Y48" s="3">
         <v>100</v>
       </c>
@@ -4734,10 +4842,10 @@
         <v>100</v>
       </c>
       <c r="AF48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>3</v>
@@ -4754,8 +4862,11 @@
       <c r="AL48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4763,7 +4874,7 @@
         <v>1900</v>
       </c>
       <c r="E49" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="F49" s="3">
         <v>2000</v>
@@ -4772,13 +4883,13 @@
         <v>2000</v>
       </c>
       <c r="H49" s="3">
-        <v>5600</v>
+        <v>2000</v>
       </c>
       <c r="I49" s="3">
         <v>5600</v>
       </c>
       <c r="J49" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="K49" s="3">
         <v>5700</v>
@@ -4790,13 +4901,13 @@
         <v>5700</v>
       </c>
       <c r="N49" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="O49" s="3">
         <v>5800</v>
       </c>
       <c r="P49" s="3">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="Q49" s="3">
         <v>6200</v>
@@ -4805,10 +4916,10 @@
         <v>6200</v>
       </c>
       <c r="S49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="T49" s="3">
         <v>6300</v>
-      </c>
-      <c r="T49" s="3">
-        <v>8500</v>
       </c>
       <c r="U49" s="3">
         <v>8500</v>
@@ -4820,7 +4931,7 @@
         <v>8500</v>
       </c>
       <c r="X49" s="3">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="Y49" s="3">
         <v>2000</v>
@@ -4832,7 +4943,7 @@
         <v>2000</v>
       </c>
       <c r="AB49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AC49" s="3">
         <v>2100</v>
@@ -4843,8 +4954,8 @@
       <c r="AE49" s="3">
         <v>2100</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>3</v>
+      <c r="AF49" s="3">
+        <v>2100</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>3</v>
@@ -4852,20 +4963,23 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2500</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4974,8 +5088,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5084,8 +5201,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5122,8 +5242,8 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -5170,15 +5290,15 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="3">
         <v>1900</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5194,8 +5314,11 @@
       <c r="AL52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5304,73 +5427,76 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E54" s="3">
         <v>8400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10100</v>
-      </c>
-      <c r="X54" s="3">
-        <v>2200</v>
       </c>
       <c r="Y54" s="3">
         <v>2200</v>
@@ -5379,43 +5505,46 @@
         <v>2200</v>
       </c>
       <c r="AA54" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="AB54" s="3">
         <v>2400</v>
       </c>
       <c r="AC54" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD54" s="3">
         <v>2500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3100</v>
       </c>
-      <c r="AG54" s="3">
-        <v>100</v>
-      </c>
       <c r="AH54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI54" s="3">
         <v>200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2500</v>
       </c>
-      <c r="AK54" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL54" s="3" t="s">
+      <c r="AL54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5454,8 +5583,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5494,40 +5624,41 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
-      </c>
-      <c r="F57" s="3">
-        <v>700</v>
       </c>
       <c r="G57" s="3">
         <v>700</v>
       </c>
       <c r="H57" s="3">
+        <v>700</v>
+      </c>
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>500</v>
       </c>
       <c r="N57" s="3">
         <v>500</v>
@@ -5539,58 +5670,58 @@
         <v>500</v>
       </c>
       <c r="Q57" s="3">
+        <v>500</v>
+      </c>
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
-      </c>
-      <c r="S57" s="3">
-        <v>600</v>
       </c>
       <c r="T57" s="3">
         <v>600</v>
       </c>
       <c r="U57" s="3">
+        <v>600</v>
+      </c>
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>800</v>
-      </c>
-      <c r="X57" s="3">
-        <v>700</v>
       </c>
       <c r="Y57" s="3">
         <v>700</v>
       </c>
       <c r="Z57" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>200</v>
       </c>
-      <c r="AF57" s="3">
-        <v>100</v>
-      </c>
       <c r="AG57" s="3">
         <v>100</v>
       </c>
       <c r="AH57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI57" s="3">
         <v>0</v>
@@ -5601,11 +5732,14 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
-      <c r="AL57" s="3" t="s">
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5619,7 +5753,7 @@
         <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
@@ -5628,7 +5762,7 @@
         <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
@@ -5640,10 +5774,10 @@
         <v>200</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5658,34 +5792,34 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>100</v>
+      </c>
+      <c r="V58" s="3">
         <v>1600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1600</v>
       </c>
-      <c r="X58" s="3">
-        <v>100</v>
-      </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>200</v>
       </c>
-      <c r="AB58" s="3">
-        <v>100</v>
-      </c>
       <c r="AC58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5699,28 +5833,31 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>3</v>
+      <c r="AH58" s="3">
+        <v>0</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AJ58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
       </c>
-      <c r="AL58" s="3" t="s">
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -5729,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3">
         <v>200</v>
@@ -5738,10 +5875,10 @@
         <v>200</v>
       </c>
       <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
@@ -5765,14 +5902,14 @@
         <v>200</v>
       </c>
       <c r="S59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T59" s="3">
+        <v>100</v>
+      </c>
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="U59" s="3">
-        <v>100</v>
-      </c>
       <c r="V59" s="3">
         <v>100</v>
       </c>
@@ -5780,28 +5917,28 @@
         <v>100</v>
       </c>
       <c r="X59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
       </c>
       <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
         <v>900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>500</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
-      </c>
       <c r="AC59" s="3">
         <v>0</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
@@ -5821,11 +5958,14 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
-      <c r="AL59" s="3" t="s">
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5833,85 +5973,85 @@
         <v>800</v>
       </c>
       <c r="E60" s="3">
+        <v>800</v>
+      </c>
+      <c r="F60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
-      </c>
-      <c r="P60" s="3">
-        <v>800</v>
       </c>
       <c r="Q60" s="3">
         <v>800</v>
       </c>
       <c r="R60" s="3">
+        <v>800</v>
+      </c>
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2700</v>
-      </c>
-      <c r="V60" s="3">
-        <v>2600</v>
       </c>
       <c r="W60" s="3">
         <v>2600</v>
       </c>
       <c r="X60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Y60" s="3">
         <v>900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>700</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>400</v>
       </c>
       <c r="AD60" s="3">
         <v>400</v>
       </c>
       <c r="AE60" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AF60" s="3">
         <v>200</v>
@@ -5920,7 +6060,7 @@
         <v>200</v>
       </c>
       <c r="AH60" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AI60" s="3">
         <v>0</v>
@@ -5931,11 +6071,14 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
-      <c r="AL60" s="3" t="s">
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5958,23 +6101,23 @@
         <v>100</v>
       </c>
       <c r="J61" s="3">
+        <v>100</v>
+      </c>
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
-        <v>100</v>
-      </c>
       <c r="L61" s="3">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>2100</v>
       </c>
       <c r="N61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
-        <v>100</v>
-      </c>
       <c r="P61" s="3">
         <v>100</v>
       </c>
@@ -5991,17 +6134,17 @@
         <v>100</v>
       </c>
       <c r="U61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V61" s="3">
         <v>200</v>
       </c>
       <c r="W61" s="3">
+        <v>200</v>
+      </c>
+      <c r="X61" s="3">
         <v>300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -6044,8 +6187,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6082,20 +6228,20 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>100</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -6112,8 +6258,8 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -6154,8 +6300,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6264,8 +6413,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6374,8 +6526,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6484,8 +6639,11 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6493,55 +6651,55 @@
         <v>900</v>
       </c>
       <c r="E66" s="3">
+        <v>900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1700</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1000</v>
       </c>
       <c r="G66" s="3">
         <v>1000</v>
       </c>
       <c r="H66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I66" s="3">
         <v>1300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1000</v>
-      </c>
-      <c r="O66" s="3">
-        <v>900</v>
       </c>
       <c r="P66" s="3">
         <v>900</v>
       </c>
       <c r="Q66" s="3">
+        <v>900</v>
+      </c>
+      <c r="R66" s="3">
         <v>1000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>900</v>
       </c>
       <c r="S66" s="3">
         <v>900</v>
       </c>
       <c r="T66" s="3">
+        <v>900</v>
+      </c>
+      <c r="U66" s="3">
         <v>1100</v>
-      </c>
-      <c r="U66" s="3">
-        <v>2800</v>
       </c>
       <c r="V66" s="3">
         <v>2800</v>
@@ -6550,28 +6708,28 @@
         <v>2800</v>
       </c>
       <c r="X66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y66" s="3">
         <v>900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>700</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>400</v>
       </c>
       <c r="AD66" s="3">
         <v>400</v>
       </c>
       <c r="AE66" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AF66" s="3">
         <v>200</v>
@@ -6580,7 +6738,7 @@
         <v>200</v>
       </c>
       <c r="AH66" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AI66" s="3">
         <v>0</v>
@@ -6591,11 +6749,14 @@
       <c r="AK66" s="3">
         <v>0</v>
       </c>
-      <c r="AL66" s="3" t="s">
+      <c r="AL66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM66" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6634,8 +6795,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6744,8 +6906,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6854,8 +7019,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6964,8 +7132,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7074,118 +7245,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-45700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-41900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-39900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-38500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-32900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-31600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-28000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-23500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-22500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-19700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-18000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-14200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-12700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-11800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-9600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-200</v>
       </c>
-      <c r="AL72" s="3" t="s">
+      <c r="AM72" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7294,8 +7471,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7404,8 +7584,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7514,118 +7697,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E76" s="3">
         <v>7500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>2400</v>
       </c>
       <c r="AE76" s="3">
         <v>2400</v>
       </c>
       <c r="AF76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AG76" s="3">
         <v>2900</v>
       </c>
-      <c r="AG76" s="3">
-        <v>0</v>
-      </c>
       <c r="AH76" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2500</v>
       </c>
-      <c r="AK76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL76" s="3" t="s">
+      <c r="AL76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7734,233 +7923,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45961</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43951</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43677</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43585</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43496</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43312</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43220</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43131</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42947</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2" t="s">
+      <c r="AM80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-1900</v>
       </c>
       <c r="K81" s="3">
         <v>-1900</v>
       </c>
       <c r="L81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M81" s="3">
         <v>-1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-500</v>
       </c>
       <c r="AE81" s="3">
         <v>-500</v>
       </c>
       <c r="AF81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="AI81" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ81" s="3">
         <v>-100</v>
       </c>
       <c r="AK81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL81" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="AL81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7999,8 +8197,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8032,7 +8231,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -8049,21 +8248,21 @@
       <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>100</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>-100</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
@@ -8086,10 +8285,10 @@
         <v>0</v>
       </c>
       <c r="AE83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>100</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
@@ -8097,11 +8296,11 @@
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AI83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AJ83" s="3" t="s">
-        <v>3</v>
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>100</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>3</v>
@@ -8109,8 +8308,11 @@
       <c r="AL83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AM83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8219,8 +8421,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8329,8 +8534,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8439,8 +8647,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8549,8 +8760,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8659,100 +8873,103 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-1300</v>
       </c>
       <c r="F89" s="3">
         <v>-1300</v>
       </c>
       <c r="G89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-300</v>
       </c>
       <c r="AD89" s="3">
         <v>-300</v>
       </c>
       <c r="AE89" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AF89" s="3">
         <v>-400</v>
       </c>
       <c r="AG89" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="AH89" s="3">
         <v>0</v>
@@ -8766,11 +8983,14 @@
       <c r="AK89" s="3">
         <v>0</v>
       </c>
-      <c r="AL89" s="3" t="s">
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8809,8 +9029,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8868,8 +9089,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -8886,8 +9107,8 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -8919,8 +9140,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9029,8 +9253,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9139,8 +9366,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9189,29 +9419,29 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -9226,11 +9456,11 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
@@ -9246,11 +9476,14 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
-      <c r="AL94" s="3" t="s">
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9289,8 +9522,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9327,8 +9561,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9399,8 +9633,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9509,8 +9746,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9619,8 +9859,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9729,44 +9972,47 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>100</v>
+      </c>
+      <c r="F100" s="3">
         <v>5300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>8700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>2100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -9774,56 +10020,56 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>400</v>
       </c>
-      <c r="AB100" s="3">
-        <v>100</v>
-      </c>
       <c r="AC100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>1500</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
@@ -9836,11 +10082,14 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
-      <c r="AL100" s="3" t="s">
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9877,8 +10126,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -9946,104 +10195,107 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
-      <c r="AL101" s="3" t="s">
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-900</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
-        <v>100</v>
-      </c>
       <c r="W102" s="3">
+        <v>100</v>
+      </c>
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>100</v>
-      </c>
       <c r="AB102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1100</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
       <c r="AH102" s="3">
         <v>0</v>
       </c>
@@ -10056,7 +10308,10 @@
       <c r="AK102" s="3">
         <v>0</v>
       </c>
-      <c r="AL102" s="3" t="s">
+      <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
